--- a/research/traditional_assets/database/data/morocco/morocco_retail_general.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_retail_general.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1195018180052069</v>
+        <v>0.1191500121875903</v>
       </c>
       <c r="C2">
-        <v>1648.53222666285</v>
+        <v>1638.400569991372</v>
       </c>
       <c r="D2">
-        <v>1509.83222666285</v>
+        <v>1517.073776393022</v>
       </c>
       <c r="E2">
-        <v>-537.9206401650194</v>
+        <v>-520.5474337633692</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>17.3732064016502</v>
       </c>
       <c r="G2">
         <v>138.7</v>
@@ -1445,28 +1445,28 @@
         <v>115.22625</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.8738722820030049</v>
       </c>
       <c r="N2">
-        <v>115.22625</v>
+        <v>114.352377717997</v>
       </c>
       <c r="O2">
-        <v>36.8724</v>
+        <v>36.59276086975904</v>
       </c>
       <c r="P2">
-        <v>78.35384999999999</v>
+        <v>77.75961684823795</v>
       </c>
       <c r="Q2">
-        <v>135.15385</v>
+        <v>134.559616848238</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1195018180052069</v>
+        <v>0.1200080527147376</v>
       </c>
       <c r="T2">
-        <v>0.9605817593200962</v>
+        <v>0.9671796946366382</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>131.8570829777203</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1191500121875903</v>
+        <v>0.1187982063699736</v>
       </c>
       <c r="C3">
-        <v>1638.400569991372</v>
+        <v>1628.338712824574</v>
       </c>
       <c r="D3">
-        <v>1517.073776393022</v>
+        <v>1524.385125627875</v>
       </c>
       <c r="E3">
-        <v>-520.5474337633692</v>
+        <v>-503.174227361719</v>
       </c>
       <c r="F3">
-        <v>17.3732064016502</v>
+        <v>34.74641280330039</v>
       </c>
       <c r="G3">
         <v>138.7</v>
@@ -1527,28 +1527,28 @@
         <v>115.22625</v>
       </c>
       <c r="M3">
-        <v>0.8738722820030049</v>
+        <v>1.74774456400601</v>
       </c>
       <c r="N3">
-        <v>114.352377717997</v>
+        <v>113.478505435994</v>
       </c>
       <c r="O3">
-        <v>36.59276086975904</v>
+        <v>36.31312173951807</v>
       </c>
       <c r="P3">
-        <v>77.75961684823795</v>
+        <v>77.16538369647591</v>
       </c>
       <c r="Q3">
-        <v>134.559616848238</v>
+        <v>133.9653836964759</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1200080527147376</v>
+        <v>0.120524618744871</v>
       </c>
       <c r="T3">
-        <v>0.9671796946366382</v>
+        <v>0.9739122816943342</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>131.8570829777203</v>
+        <v>65.92854148886013</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1187982063699736</v>
+        <v>0.1184464005523569</v>
       </c>
       <c r="C4">
-        <v>1628.338712824574</v>
+        <v>1618.347669219795</v>
       </c>
       <c r="D4">
-        <v>1524.385125627875</v>
+        <v>1531.767288424745</v>
       </c>
       <c r="E4">
-        <v>-503.174227361719</v>
+        <v>-485.8010209600689</v>
       </c>
       <c r="F4">
-        <v>34.74641280330039</v>
+        <v>52.11961920495058</v>
       </c>
       <c r="G4">
         <v>138.7</v>
@@ -1609,28 +1609,28 @@
         <v>115.22625</v>
       </c>
       <c r="M4">
-        <v>1.74774456400601</v>
+        <v>2.621616846009014</v>
       </c>
       <c r="N4">
-        <v>113.478505435994</v>
+        <v>112.604633153991</v>
       </c>
       <c r="O4">
-        <v>36.31312173951807</v>
+        <v>36.03348260927712</v>
       </c>
       <c r="P4">
-        <v>77.16538369647591</v>
+        <v>76.57115054471386</v>
       </c>
       <c r="Q4">
-        <v>133.9653836964759</v>
+        <v>133.3711505447139</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.120524618744871</v>
+        <v>0.1210518356209865</v>
       </c>
       <c r="T4">
-        <v>0.9739122816943342</v>
+        <v>0.980783684980024</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>65.92854148886013</v>
+        <v>43.95236099257344</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1184464005523569</v>
+        <v>0.1180945947347403</v>
       </c>
       <c r="C5">
-        <v>1618.347669219795</v>
+        <v>1608.428472973123</v>
       </c>
       <c r="D5">
-        <v>1531.767288424745</v>
+        <v>1539.221298579723</v>
       </c>
       <c r="E5">
-        <v>-485.8010209600689</v>
+        <v>-468.4278145584187</v>
       </c>
       <c r="F5">
-        <v>52.11961920495058</v>
+        <v>69.49282560660079</v>
       </c>
       <c r="G5">
         <v>138.7</v>
@@ -1691,28 +1691,28 @@
         <v>115.22625</v>
       </c>
       <c r="M5">
-        <v>2.621616846009014</v>
+        <v>3.49548912801202</v>
       </c>
       <c r="N5">
-        <v>112.604633153991</v>
+        <v>111.730760871988</v>
       </c>
       <c r="O5">
-        <v>36.03348260927712</v>
+        <v>35.75384347903615</v>
       </c>
       <c r="P5">
-        <v>76.57115054471386</v>
+        <v>75.97691739295182</v>
       </c>
       <c r="Q5">
-        <v>133.3711505447139</v>
+        <v>132.7769173929518</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1210518356209865</v>
+        <v>0.1215900361820211</v>
       </c>
       <c r="T5">
-        <v>0.980783684980024</v>
+        <v>0.9877982425008321</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>43.95236099257344</v>
+        <v>32.96427074443007</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1180945947347403</v>
+        <v>0.1177427889171236</v>
       </c>
       <c r="C6">
-        <v>1608.428472973123</v>
+        <v>1598.582178102017</v>
       </c>
       <c r="D6">
-        <v>1539.221298579723</v>
+        <v>1546.748210110268</v>
       </c>
       <c r="E6">
-        <v>-468.4278145584187</v>
+        <v>-451.0546081567685</v>
       </c>
       <c r="F6">
-        <v>69.49282560660079</v>
+        <v>86.86603200825098</v>
       </c>
       <c r="G6">
         <v>138.7</v>
@@ -1773,28 +1773,28 @@
         <v>115.22625</v>
       </c>
       <c r="M6">
-        <v>3.49548912801202</v>
+        <v>4.369361410015024</v>
       </c>
       <c r="N6">
-        <v>111.730760871988</v>
+        <v>110.856888589985</v>
       </c>
       <c r="O6">
-        <v>35.75384347903615</v>
+        <v>35.47420434879519</v>
       </c>
       <c r="P6">
-        <v>75.97691739295182</v>
+        <v>75.38268424118979</v>
       </c>
       <c r="Q6">
-        <v>132.7769173929518</v>
+        <v>132.1826842411898</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1215900361820211</v>
+        <v>0.1221395672811827</v>
       </c>
       <c r="T6">
-        <v>0.9877982425008321</v>
+        <v>0.9949604749168155</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.96427074443007</v>
+        <v>26.37141659554406</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1177427889171236</v>
+        <v>0.1173909830995069</v>
       </c>
       <c r="C7">
-        <v>1598.582178102017</v>
+        <v>1588.809859342161</v>
       </c>
       <c r="D7">
-        <v>1546.748210110268</v>
+        <v>1554.349097752062</v>
       </c>
       <c r="E7">
-        <v>-451.0546081567685</v>
+        <v>-433.6814017551183</v>
       </c>
       <c r="F7">
-        <v>86.86603200825098</v>
+        <v>104.2392384099012</v>
       </c>
       <c r="G7">
         <v>138.7</v>
@@ -1855,28 +1855,28 @@
         <v>115.22625</v>
       </c>
       <c r="M7">
-        <v>4.369361410015024</v>
+        <v>5.243233692018029</v>
       </c>
       <c r="N7">
-        <v>110.856888589985</v>
+        <v>109.983016307982</v>
       </c>
       <c r="O7">
-        <v>35.47420434879519</v>
+        <v>35.19456521855423</v>
       </c>
       <c r="P7">
-        <v>75.38268424118979</v>
+        <v>74.78845108942774</v>
       </c>
       <c r="Q7">
-        <v>132.1826842411898</v>
+        <v>131.5884510894277</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1221395672811827</v>
+        <v>0.1227007905313904</v>
       </c>
       <c r="T7">
-        <v>0.9949604749168155</v>
+        <v>1.002275095256543</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.37141659554406</v>
+        <v>21.97618049628672</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1173909830995069</v>
+        <v>0.1170391772818903</v>
       </c>
       <c r="C8">
-        <v>1588.809859342161</v>
+        <v>1579.112612659032</v>
       </c>
       <c r="D8">
-        <v>1554.349097752062</v>
+        <v>1562.025057470583</v>
       </c>
       <c r="E8">
-        <v>-433.6814017551183</v>
+        <v>-416.3081953534681</v>
       </c>
       <c r="F8">
-        <v>104.2392384099012</v>
+        <v>121.6124448115514</v>
       </c>
       <c r="G8">
         <v>138.7</v>
@@ -1937,28 +1937,28 @@
         <v>115.22625</v>
       </c>
       <c r="M8">
-        <v>5.243233692018028</v>
+        <v>6.117105974021033</v>
       </c>
       <c r="N8">
-        <v>109.983016307982</v>
+        <v>109.109144025979</v>
       </c>
       <c r="O8">
-        <v>35.19456521855423</v>
+        <v>34.91492608831327</v>
       </c>
       <c r="P8">
-        <v>74.78845108942774</v>
+        <v>74.19421793766568</v>
       </c>
       <c r="Q8">
-        <v>131.5884510894277</v>
+        <v>130.9942179376657</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1227007905313904</v>
+        <v>0.1232740830988067</v>
       </c>
       <c r="T8">
-        <v>1.002275095256543</v>
+        <v>1.00974701925949</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.97618049628672</v>
+        <v>18.83672613967433</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1170391772818903</v>
+        <v>0.1166873714642736</v>
       </c>
       <c r="C9">
-        <v>1579.112612659032</v>
+        <v>1569.491555774706</v>
       </c>
       <c r="D9">
-        <v>1562.025057470583</v>
+        <v>1569.777206987907</v>
       </c>
       <c r="E9">
-        <v>-416.3081953534681</v>
+        <v>-398.9349889518179</v>
       </c>
       <c r="F9">
-        <v>121.6124448115514</v>
+        <v>138.9856512132016</v>
       </c>
       <c r="G9">
         <v>138.7</v>
@@ -2019,28 +2019,28 @@
         <v>115.22625</v>
       </c>
       <c r="M9">
-        <v>6.117105974021034</v>
+        <v>6.990978256024039</v>
       </c>
       <c r="N9">
-        <v>109.109144025979</v>
+        <v>108.235271743976</v>
       </c>
       <c r="O9">
-        <v>34.91492608831327</v>
+        <v>34.63528695807231</v>
       </c>
       <c r="P9">
-        <v>74.19421793766568</v>
+        <v>73.59998478590364</v>
       </c>
       <c r="Q9">
-        <v>130.9942179376657</v>
+        <v>130.3999847859037</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1232740830988067</v>
+        <v>0.1238598385481235</v>
       </c>
       <c r="T9">
-        <v>1.00974701925949</v>
+        <v>1.017381376392937</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.83672613967433</v>
+        <v>16.48213537221503</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1166873714642736</v>
+        <v>0.116335565646657</v>
       </c>
       <c r="C10">
-        <v>1569.491555774706</v>
+        <v>1559.947828710428</v>
       </c>
       <c r="D10">
-        <v>1569.777206987907</v>
+        <v>1577.606686325279</v>
       </c>
       <c r="E10">
-        <v>-398.9349889518179</v>
+        <v>-381.5617825501677</v>
       </c>
       <c r="F10">
-        <v>138.9856512132016</v>
+        <v>156.3588576148518</v>
       </c>
       <c r="G10">
         <v>138.7</v>
@@ -2101,28 +2101,28 @@
         <v>115.22625</v>
       </c>
       <c r="M10">
-        <v>6.990978256024039</v>
+        <v>7.864850538027043</v>
       </c>
       <c r="N10">
-        <v>108.235271743976</v>
+        <v>107.361399461973</v>
       </c>
       <c r="O10">
-        <v>34.63528695807231</v>
+        <v>34.35564782783135</v>
       </c>
       <c r="P10">
-        <v>73.59998478590364</v>
+        <v>73.0057516341416</v>
       </c>
       <c r="Q10">
-        <v>130.3999847859037</v>
+        <v>129.8057516341416</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1238598385481235</v>
+        <v>0.1244584677435791</v>
       </c>
       <c r="T10">
-        <v>1.017381376392937</v>
+        <v>1.02518352159525</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.48213537221503</v>
+        <v>14.65078699752448</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.116335565646657</v>
+        <v>0.1159837598290403</v>
       </c>
       <c r="C11">
-        <v>1559.947828710428</v>
+        <v>1550.482594345501</v>
       </c>
       <c r="D11">
-        <v>1577.606686325279</v>
+        <v>1585.514658362003</v>
       </c>
       <c r="E11">
-        <v>-381.5617825501677</v>
+        <v>-364.1885761485175</v>
       </c>
       <c r="F11">
-        <v>156.3588576148518</v>
+        <v>173.7320640165019</v>
       </c>
       <c r="G11">
         <v>138.7</v>
@@ -2183,28 +2183,28 @@
         <v>115.22625</v>
       </c>
       <c r="M11">
-        <v>7.864850538027043</v>
+        <v>8.738722820030047</v>
       </c>
       <c r="N11">
-        <v>107.361399461973</v>
+        <v>106.4875271799699</v>
       </c>
       <c r="O11">
-        <v>34.35564782783135</v>
+        <v>34.07600869759038</v>
       </c>
       <c r="P11">
-        <v>73.0057516341416</v>
+        <v>72.41151848237956</v>
       </c>
       <c r="Q11">
-        <v>129.8057516341416</v>
+        <v>129.2115184823796</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1244584677435791</v>
+        <v>0.1250703998100448</v>
       </c>
       <c r="T11">
-        <v>1.02518352159525</v>
+        <v>1.033159047802059</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.65078699752448</v>
+        <v>13.18570829777203</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1159837598290403</v>
+        <v>0.1157441540114236</v>
       </c>
       <c r="C12">
-        <v>1550.482594345501</v>
+        <v>1538.540843101604</v>
       </c>
       <c r="D12">
-        <v>1585.514658362003</v>
+        <v>1590.946113519756</v>
       </c>
       <c r="E12">
-        <v>-364.1885761485175</v>
+        <v>-346.8153697468673</v>
       </c>
       <c r="F12">
-        <v>173.732064016502</v>
+        <v>191.1052704181521</v>
       </c>
       <c r="G12">
         <v>138.7</v>
@@ -2265,45 +2265,45 @@
         <v>115.22625</v>
       </c>
       <c r="M12">
-        <v>8.738722820030048</v>
+        <v>9.899253007660281</v>
       </c>
       <c r="N12">
-        <v>106.4875271799699</v>
+        <v>105.3269969923397</v>
       </c>
       <c r="O12">
-        <v>34.07600869759038</v>
+        <v>33.70463903754871</v>
       </c>
       <c r="P12">
-        <v>72.41151848237956</v>
+        <v>71.622357954791</v>
       </c>
       <c r="Q12">
-        <v>129.2115184823796</v>
+        <v>128.422357954791</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1250703998100448</v>
+        <v>0.125696083158903</v>
       </c>
       <c r="T12">
-        <v>1.033159047802059</v>
+        <v>1.041313799316886</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.32</v>
       </c>
       <c r="W12">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.18570829777203</v>
+        <v>11.63989342537615</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1157441540114236</v>
+        <v>0.115402548193807</v>
       </c>
       <c r="C13">
-        <v>1538.540843101604</v>
+        <v>1528.97592047686</v>
       </c>
       <c r="D13">
-        <v>1590.946113519756</v>
+        <v>1598.754397296662</v>
       </c>
       <c r="E13">
-        <v>-346.8153697468673</v>
+        <v>-329.4421633452171</v>
       </c>
       <c r="F13">
-        <v>191.1052704181521</v>
+        <v>208.4784768198023</v>
       </c>
       <c r="G13">
         <v>138.7</v>
@@ -2347,28 +2347,28 @@
         <v>115.22625</v>
       </c>
       <c r="M13">
-        <v>9.899253007660281</v>
+        <v>10.79918509926576</v>
       </c>
       <c r="N13">
-        <v>105.3269969923397</v>
+        <v>104.4270649007342</v>
       </c>
       <c r="O13">
-        <v>33.70463903754871</v>
+        <v>33.41666076823496</v>
       </c>
       <c r="P13">
-        <v>71.622357954791</v>
+        <v>71.01040413249927</v>
       </c>
       <c r="Q13">
-        <v>128.422357954791</v>
+        <v>127.8104041324993</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.125696083158903</v>
+        <v>0.1263359865838715</v>
       </c>
       <c r="T13">
-        <v>1.041313799316886</v>
+        <v>1.049653886093414</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.63989342537615</v>
+        <v>10.66990230659481</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.115402548193807</v>
+        <v>0.1150609423761903</v>
       </c>
       <c r="C14">
-        <v>1528.97592047686</v>
+        <v>1519.488021209646</v>
       </c>
       <c r="D14">
-        <v>1598.754397296662</v>
+        <v>1606.639704431098</v>
       </c>
       <c r="E14">
-        <v>-329.4421633452171</v>
+        <v>-312.0689569435669</v>
       </c>
       <c r="F14">
-        <v>208.4784768198023</v>
+        <v>225.8516832214526</v>
       </c>
       <c r="G14">
         <v>138.7</v>
@@ -2429,28 +2429,28 @@
         <v>115.22625</v>
       </c>
       <c r="M14">
-        <v>10.79918509926576</v>
+        <v>11.69911719087124</v>
       </c>
       <c r="N14">
-        <v>104.4270649007342</v>
+        <v>103.5271328091287</v>
       </c>
       <c r="O14">
-        <v>33.41666076823496</v>
+        <v>33.1286824989212</v>
       </c>
       <c r="P14">
-        <v>71.01040413249927</v>
+        <v>70.39845031020755</v>
       </c>
       <c r="Q14">
-        <v>127.8104041324993</v>
+        <v>127.1984503102076</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1263359865838715</v>
+        <v>0.1269906004324027</v>
       </c>
       <c r="T14">
-        <v>1.049653886093414</v>
+        <v>1.058185699002736</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.66990230659481</v>
+        <v>9.849140590702897</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1150609423761903</v>
+        <v>0.1148811765585736</v>
       </c>
       <c r="C15">
-        <v>1519.488021209646</v>
+        <v>1506.295677301522</v>
       </c>
       <c r="D15">
-        <v>1606.639704431098</v>
+        <v>1610.820566924625</v>
       </c>
       <c r="E15">
-        <v>-312.0689569435669</v>
+        <v>-294.6957505419167</v>
       </c>
       <c r="F15">
-        <v>225.8516832214526</v>
+        <v>243.2248896231028</v>
       </c>
       <c r="G15">
         <v>138.7</v>
@@ -2511,45 +2511,45 @@
         <v>115.22625</v>
       </c>
       <c r="M15">
-        <v>11.69911719087124</v>
+        <v>13.012531594836</v>
       </c>
       <c r="N15">
-        <v>103.5271328091287</v>
+        <v>102.213718405164</v>
       </c>
       <c r="O15">
-        <v>33.1286824989212</v>
+        <v>32.70838988965248</v>
       </c>
       <c r="P15">
-        <v>70.39845031020755</v>
+        <v>69.50532851551152</v>
       </c>
       <c r="Q15">
-        <v>127.1984503102076</v>
+        <v>126.3053285155115</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1269906004324027</v>
+        <v>0.1276604378588066</v>
       </c>
       <c r="T15">
-        <v>1.058185699002736</v>
+        <v>1.066915926165763</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.32</v>
       </c>
       <c r="W15">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>9.849140590702897</v>
+        <v>8.85502172734223</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1148811765585736</v>
+        <v>0.114551130740957</v>
       </c>
       <c r="C16">
-        <v>1506.295677301522</v>
+        <v>1496.655355949393</v>
       </c>
       <c r="D16">
-        <v>1610.820566924625</v>
+        <v>1618.553451974145</v>
       </c>
       <c r="E16">
-        <v>-294.6957505419167</v>
+        <v>-277.3225441402665</v>
       </c>
       <c r="F16">
-        <v>243.2248896231028</v>
+        <v>260.598096024753</v>
       </c>
       <c r="G16">
         <v>138.7</v>
@@ -2593,28 +2593,28 @@
         <v>115.22625</v>
       </c>
       <c r="M16">
-        <v>13.012531594836</v>
+        <v>13.94199813732428</v>
       </c>
       <c r="N16">
-        <v>102.213718405164</v>
+        <v>101.2842518626757</v>
       </c>
       <c r="O16">
-        <v>32.70838988965248</v>
+        <v>32.41096059605623</v>
       </c>
       <c r="P16">
-        <v>69.50532851551152</v>
+        <v>68.87329126661949</v>
       </c>
       <c r="Q16">
-        <v>126.3053285155115</v>
+        <v>125.6732912666195</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1276604378588066</v>
+        <v>0.1283460361658318</v>
       </c>
       <c r="T16">
-        <v>1.066915926165763</v>
+        <v>1.075851570438508</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.85502172734223</v>
+        <v>8.264686945519415</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.114551130740957</v>
+        <v>0.1142210849233403</v>
       </c>
       <c r="C17">
-        <v>1496.655355949393</v>
+        <v>1487.089637517446</v>
       </c>
       <c r="D17">
-        <v>1618.553451974145</v>
+        <v>1626.360939943849</v>
       </c>
       <c r="E17">
-        <v>-277.3225441402665</v>
+        <v>-259.9493377386163</v>
       </c>
       <c r="F17">
-        <v>260.5980960247529</v>
+        <v>277.9713024264032</v>
       </c>
       <c r="G17">
         <v>138.7</v>
@@ -2675,28 +2675,28 @@
         <v>115.22625</v>
       </c>
       <c r="M17">
-        <v>13.94199813732428</v>
+        <v>14.87146467981257</v>
       </c>
       <c r="N17">
-        <v>101.2842518626757</v>
+        <v>100.3547853201874</v>
       </c>
       <c r="O17">
-        <v>32.41096059605623</v>
+        <v>32.11353130245998</v>
       </c>
       <c r="P17">
-        <v>68.87329126661949</v>
+        <v>68.24125401772746</v>
       </c>
       <c r="Q17">
-        <v>125.6732912666195</v>
+        <v>125.0412540177275</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1283460361658318</v>
+        <v>0.1290479582420718</v>
       </c>
       <c r="T17">
-        <v>1.075851570438508</v>
+        <v>1.084999968146318</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.264686945519415</v>
+        <v>7.748144011424452</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1142210849233403</v>
+        <v>0.1139835191057237</v>
       </c>
       <c r="C18">
-        <v>1487.089637517446</v>
+        <v>1475.38301699322</v>
       </c>
       <c r="D18">
-        <v>1626.360939943849</v>
+        <v>1632.027525821274</v>
       </c>
       <c r="E18">
-        <v>-259.9493377386163</v>
+        <v>-242.5761313369661</v>
       </c>
       <c r="F18">
-        <v>277.9713024264032</v>
+        <v>295.3445088280533</v>
       </c>
       <c r="G18">
         <v>138.7</v>
@@ -2757,45 +2757,45 @@
         <v>115.22625</v>
       </c>
       <c r="M18">
-        <v>14.87146467981257</v>
+        <v>16.0372068293633</v>
       </c>
       <c r="N18">
-        <v>100.3547853201874</v>
+        <v>99.18904317063669</v>
       </c>
       <c r="O18">
-        <v>32.11353130245998</v>
+        <v>31.74049381460374</v>
       </c>
       <c r="P18">
-        <v>68.24125401772746</v>
+        <v>67.44854935603296</v>
       </c>
       <c r="Q18">
-        <v>125.0412540177275</v>
+        <v>124.248549356033</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1290479582420718</v>
+        <v>0.1297667941032815</v>
       </c>
       <c r="T18">
-        <v>1.084999968146318</v>
+        <v>1.094368809172389</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.32</v>
       </c>
       <c r="W18">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.748144011424452</v>
+        <v>7.184932589946192</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1139835191057237</v>
+        <v>0.113658913288107</v>
       </c>
       <c r="C19">
-        <v>1475.38301699322</v>
+        <v>1465.816679339128</v>
       </c>
       <c r="D19">
-        <v>1632.027525821274</v>
+        <v>1639.834394568831</v>
       </c>
       <c r="E19">
-        <v>-242.5761313369661</v>
+        <v>-225.2029249353159</v>
       </c>
       <c r="F19">
-        <v>295.3445088280533</v>
+        <v>312.7177152297036</v>
       </c>
       <c r="G19">
         <v>138.7</v>
@@ -2839,28 +2839,28 @@
         <v>115.22625</v>
       </c>
       <c r="M19">
-        <v>16.0372068293633</v>
+        <v>16.9805719369729</v>
       </c>
       <c r="N19">
-        <v>99.18904317063669</v>
+        <v>98.24567806302709</v>
       </c>
       <c r="O19">
-        <v>31.74049381460374</v>
+        <v>31.43861698016867</v>
       </c>
       <c r="P19">
-        <v>67.44854935603296</v>
+        <v>66.80706108285841</v>
       </c>
       <c r="Q19">
-        <v>124.248549356033</v>
+        <v>123.6070610828584</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1297667941032815</v>
+        <v>0.1305031625464719</v>
       </c>
       <c r="T19">
-        <v>1.094368809172389</v>
+        <v>1.103966158516169</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.184932589946192</v>
+        <v>6.785769668282514</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.113658913288107</v>
+        <v>0.1133343074704904</v>
       </c>
       <c r="C20">
-        <v>1465.816679339127</v>
+        <v>1456.325389615715</v>
       </c>
       <c r="D20">
-        <v>1639.834394568831</v>
+        <v>1647.716311247068</v>
       </c>
       <c r="E20">
-        <v>-225.2029249353159</v>
+        <v>-207.8297185336658</v>
       </c>
       <c r="F20">
-        <v>312.7177152297035</v>
+        <v>330.0909216313537</v>
       </c>
       <c r="G20">
         <v>138.7</v>
@@ -2921,28 +2921,28 @@
         <v>115.22625</v>
       </c>
       <c r="M20">
-        <v>16.9805719369729</v>
+        <v>17.92393704458251</v>
       </c>
       <c r="N20">
-        <v>98.2456780630271</v>
+        <v>97.30231295541749</v>
       </c>
       <c r="O20">
-        <v>31.43861698016867</v>
+        <v>31.1367401457336</v>
       </c>
       <c r="P20">
-        <v>66.80706108285843</v>
+        <v>66.16557280968389</v>
       </c>
       <c r="Q20">
-        <v>123.6070610828584</v>
+        <v>122.9655728096839</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1305031625464719</v>
+        <v>0.1312577129265313</v>
       </c>
       <c r="T20">
-        <v>1.103966158516169</v>
+        <v>1.113800479448684</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.785769668282516</v>
+        <v>6.428623896267647</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1133343074704904</v>
+        <v>0.1131457016528737</v>
       </c>
       <c r="C21">
-        <v>1456.325389615715</v>
+        <v>1443.566715017222</v>
       </c>
       <c r="D21">
-        <v>1647.716311247068</v>
+        <v>1652.330843050226</v>
       </c>
       <c r="E21">
-        <v>-207.8297185336658</v>
+        <v>-190.4565121320155</v>
       </c>
       <c r="F21">
-        <v>330.0909216313537</v>
+        <v>347.4641280330039</v>
       </c>
       <c r="G21">
         <v>138.7</v>
@@ -3003,45 +3003,45 @@
         <v>115.22625</v>
       </c>
       <c r="M21">
-        <v>17.92393704458251</v>
+        <v>19.21476628022512</v>
       </c>
       <c r="N21">
-        <v>97.30231295541749</v>
+        <v>96.01148371977487</v>
       </c>
       <c r="O21">
-        <v>31.1367401457336</v>
+        <v>30.72367479032796</v>
       </c>
       <c r="P21">
-        <v>66.16557280968389</v>
+        <v>65.28780892944691</v>
       </c>
       <c r="Q21">
-        <v>122.9655728096839</v>
+        <v>122.0878089294469</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1312577129265313</v>
+        <v>0.1320311270660921</v>
       </c>
       <c r="T21">
-        <v>1.113800479448684</v>
+        <v>1.123880658404512</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.32</v>
       </c>
       <c r="W21">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.428623896267647</v>
+        <v>5.996755220415308</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1131457016528737</v>
+        <v>0.112827895835257</v>
       </c>
       <c r="C22">
-        <v>1443.566715017222</v>
+        <v>1434.027863968743</v>
       </c>
       <c r="D22">
-        <v>1652.330843050226</v>
+        <v>1660.165198403397</v>
       </c>
       <c r="E22">
-        <v>-190.4565121320155</v>
+        <v>-173.0833057303653</v>
       </c>
       <c r="F22">
-        <v>347.4641280330039</v>
+        <v>364.8373344346541</v>
       </c>
       <c r="G22">
         <v>138.7</v>
@@ -3085,28 +3085,28 @@
         <v>115.22625</v>
       </c>
       <c r="M22">
-        <v>19.21476628022512</v>
+        <v>20.17550459423637</v>
       </c>
       <c r="N22">
-        <v>96.01148371977487</v>
+        <v>95.05074540576362</v>
       </c>
       <c r="O22">
-        <v>30.72367479032796</v>
+        <v>30.41623852984436</v>
       </c>
       <c r="P22">
-        <v>65.28780892944691</v>
+        <v>64.63450687591926</v>
       </c>
       <c r="Q22">
-        <v>122.0878089294469</v>
+        <v>121.4345068759193</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1320311270660921</v>
+        <v>0.1328241213104519</v>
       </c>
       <c r="T22">
-        <v>1.123880658404512</v>
+        <v>1.134216031764286</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.996755220415308</v>
+        <v>5.711195448014579</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.112827895835257</v>
+        <v>0.1125100900176403</v>
       </c>
       <c r="C23">
-        <v>1434.027863968743</v>
+        <v>1424.563658411161</v>
       </c>
       <c r="D23">
-        <v>1660.165198403397</v>
+        <v>1668.074199247465</v>
       </c>
       <c r="E23">
-        <v>-173.0833057303653</v>
+        <v>-155.7100993287152</v>
       </c>
       <c r="F23">
-        <v>364.8373344346541</v>
+        <v>382.2105408363043</v>
       </c>
       <c r="G23">
         <v>138.7</v>
@@ -3167,28 +3167,28 @@
         <v>115.22625</v>
       </c>
       <c r="M23">
-        <v>20.17550459423637</v>
+        <v>21.13624290824763</v>
       </c>
       <c r="N23">
-        <v>95.05074540576362</v>
+        <v>94.09000709175237</v>
       </c>
       <c r="O23">
-        <v>30.41623852984436</v>
+        <v>30.10880226936076</v>
       </c>
       <c r="P23">
-        <v>64.63450687591926</v>
+        <v>63.98120482239161</v>
       </c>
       <c r="Q23">
-        <v>121.4345068759193</v>
+        <v>120.7812048223916</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1328241213104519</v>
+        <v>0.1336374487405645</v>
       </c>
       <c r="T23">
-        <v>1.134216031764286</v>
+        <v>1.144816414697386</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.711195448014579</v>
+        <v>5.451595654923008</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1125100900176403</v>
+        <v>0.1121922842000237</v>
       </c>
       <c r="C24">
-        <v>1424.563658411161</v>
+        <v>1415.175170280988</v>
       </c>
       <c r="D24">
-        <v>1668.074199247465</v>
+        <v>1676.058917518943</v>
       </c>
       <c r="E24">
-        <v>-155.7100993287152</v>
+        <v>-138.3368929270649</v>
       </c>
       <c r="F24">
-        <v>382.2105408363043</v>
+        <v>399.5837472379545</v>
       </c>
       <c r="G24">
         <v>138.7</v>
@@ -3249,28 +3249,28 @@
         <v>115.22625</v>
       </c>
       <c r="M24">
-        <v>21.13624290824763</v>
+        <v>22.09698122225889</v>
       </c>
       <c r="N24">
-        <v>94.09000709175237</v>
+        <v>93.1292687777411</v>
       </c>
       <c r="O24">
-        <v>30.10880226936076</v>
+        <v>29.80136600887715</v>
       </c>
       <c r="P24">
-        <v>63.98120482239161</v>
+        <v>63.32790276886395</v>
       </c>
       <c r="Q24">
-        <v>120.7812048223916</v>
+        <v>120.127902768864</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1336374487405645</v>
+        <v>0.1344719015584723</v>
       </c>
       <c r="T24">
-        <v>1.144816414697386</v>
+        <v>1.155692132252126</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.451595654923008</v>
+        <v>5.214569756882875</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1121922842000237</v>
+        <v>0.111874478382407</v>
       </c>
       <c r="C25">
-        <v>1415.175170280988</v>
+        <v>1405.863492137996</v>
       </c>
       <c r="D25">
-        <v>1676.058917518943</v>
+        <v>1684.1204457776</v>
       </c>
       <c r="E25">
-        <v>-138.3368929270649</v>
+        <v>-120.9636865254147</v>
       </c>
       <c r="F25">
-        <v>399.5837472379545</v>
+        <v>416.9569536396047</v>
       </c>
       <c r="G25">
         <v>138.7</v>
@@ -3331,28 +3331,28 @@
         <v>115.22625</v>
       </c>
       <c r="M25">
-        <v>22.09698122225889</v>
+        <v>23.05771953627014</v>
       </c>
       <c r="N25">
-        <v>93.1292687777411</v>
+        <v>92.16853046372985</v>
       </c>
       <c r="O25">
-        <v>29.80136600887715</v>
+        <v>29.49392974839355</v>
       </c>
       <c r="P25">
-        <v>63.32790276886395</v>
+        <v>62.6746007153363</v>
       </c>
       <c r="Q25">
-        <v>120.127902768864</v>
+        <v>119.4746007153363</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1344719015584723</v>
+        <v>0.1353283136610619</v>
       </c>
       <c r="T25">
-        <v>1.155692132252126</v>
+        <v>1.166854052900411</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.214569756882875</v>
+        <v>4.997296017012756</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.111874478382407</v>
+        <v>0.1115566725647903</v>
       </c>
       <c r="C26">
-        <v>1405.863492137996</v>
+        <v>1396.629737663569</v>
       </c>
       <c r="D26">
-        <v>1684.1204457776</v>
+        <v>1692.259897704824</v>
       </c>
       <c r="E26">
-        <v>-120.9636865254148</v>
+        <v>-103.5904801237646</v>
       </c>
       <c r="F26">
-        <v>416.9569536396046</v>
+        <v>434.3301600412549</v>
       </c>
       <c r="G26">
         <v>138.7</v>
@@ -3413,28 +3413,28 @@
         <v>115.22625</v>
       </c>
       <c r="M26">
-        <v>23.05771953627014</v>
+        <v>24.0184578502814</v>
       </c>
       <c r="N26">
-        <v>92.16853046372985</v>
+        <v>91.2077921497186</v>
       </c>
       <c r="O26">
-        <v>29.49392974839355</v>
+        <v>29.18649348790995</v>
       </c>
       <c r="P26">
-        <v>62.6746007153363</v>
+        <v>62.02129866180864</v>
       </c>
       <c r="Q26">
-        <v>119.4746007153363</v>
+        <v>118.8212986618087</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1353283136610619</v>
+        <v>0.1362075634197205</v>
       </c>
       <c r="T26">
-        <v>1.166854052900411</v>
+        <v>1.178313624765984</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.997296017012757</v>
+        <v>4.797404176332247</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1115566725647903</v>
+        <v>0.1112388667471737</v>
       </c>
       <c r="C27">
-        <v>1396.629737663569</v>
+        <v>1387.475042173604</v>
       </c>
       <c r="D27">
-        <v>1692.259897704824</v>
+        <v>1700.478408616509</v>
       </c>
       <c r="E27">
-        <v>-103.5904801237646</v>
+        <v>-86.21727372211433</v>
       </c>
       <c r="F27">
-        <v>434.3301600412549</v>
+        <v>451.7033664429051</v>
       </c>
       <c r="G27">
         <v>138.7</v>
@@ -3495,28 +3495,28 @@
         <v>115.22625</v>
       </c>
       <c r="M27">
-        <v>24.0184578502814</v>
+        <v>24.97919616429265</v>
       </c>
       <c r="N27">
-        <v>91.2077921497186</v>
+        <v>90.24705383570733</v>
       </c>
       <c r="O27">
-        <v>29.18649348790995</v>
+        <v>28.87905722742635</v>
       </c>
       <c r="P27">
-        <v>62.02129866180864</v>
+        <v>61.36799660828099</v>
       </c>
       <c r="Q27">
-        <v>118.8212986618087</v>
+        <v>118.167996608281</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1362075634197205</v>
+        <v>0.1371105766853699</v>
       </c>
       <c r="T27">
-        <v>1.178313624765984</v>
+        <v>1.190082914790087</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.797404176332247</v>
+        <v>4.612888631088698</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1112388667471737</v>
+        <v>0.111380060929557</v>
       </c>
       <c r="C28">
-        <v>1387.475042173604</v>
+        <v>1366.440697688794</v>
       </c>
       <c r="D28">
-        <v>1700.478408616509</v>
+        <v>1696.81727053335</v>
       </c>
       <c r="E28">
-        <v>-86.21727372211433</v>
+        <v>-68.84406732046415</v>
       </c>
       <c r="F28">
-        <v>451.7033664429051</v>
+        <v>469.0765728445553</v>
       </c>
       <c r="G28">
         <v>138.7</v>
@@ -3577,45 +3577,45 @@
         <v>115.22625</v>
       </c>
       <c r="M28">
-        <v>24.97919616429265</v>
+        <v>27.1126259104153</v>
       </c>
       <c r="N28">
-        <v>90.24705383570733</v>
+        <v>88.11362408958469</v>
       </c>
       <c r="O28">
-        <v>28.87905722742635</v>
+        <v>28.1963597086671</v>
       </c>
       <c r="P28">
-        <v>61.36799660828099</v>
+        <v>59.91726438091759</v>
       </c>
       <c r="Q28">
-        <v>118.167996608281</v>
+        <v>116.7172643809176</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1371105766853699</v>
+        <v>0.1380383300404891</v>
       </c>
       <c r="T28">
-        <v>1.190082914790087</v>
+        <v>1.202174651116219</v>
       </c>
       <c r="U28">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.32</v>
       </c>
       <c r="W28">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.612888631088698</v>
+        <v>4.249911107125035</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.111380060929557</v>
+        <v>0.1110792551119404</v>
       </c>
       <c r="C29">
-        <v>1366.440697688794</v>
+        <v>1356.886399538067</v>
       </c>
       <c r="D29">
-        <v>1696.81727053335</v>
+        <v>1704.636178784273</v>
       </c>
       <c r="E29">
-        <v>-68.84406732046415</v>
+        <v>-51.47086091881391</v>
       </c>
       <c r="F29">
-        <v>469.0765728445553</v>
+        <v>486.4497792462055</v>
       </c>
       <c r="G29">
         <v>138.7</v>
@@ -3659,28 +3659,28 @@
         <v>115.22625</v>
       </c>
       <c r="M29">
-        <v>27.1126259104153</v>
+        <v>28.11679724043068</v>
       </c>
       <c r="N29">
-        <v>88.11362408958469</v>
+        <v>87.10945275956931</v>
       </c>
       <c r="O29">
-        <v>28.1963597086671</v>
+        <v>27.87502488306218</v>
       </c>
       <c r="P29">
-        <v>59.91726438091759</v>
+        <v>59.23442787650713</v>
       </c>
       <c r="Q29">
-        <v>116.7172643809176</v>
+        <v>116.0344278765071</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1380383300404891</v>
+        <v>0.1389918543221394</v>
       </c>
       <c r="T29">
-        <v>1.202174651116219</v>
+        <v>1.214602269006966</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.249911107125035</v>
+        <v>4.098128567584855</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1110792551119404</v>
+        <v>0.1114686492943237</v>
       </c>
       <c r="C30">
-        <v>1356.886399538067</v>
+        <v>1329.405243327312</v>
       </c>
       <c r="D30">
-        <v>1704.636178784273</v>
+        <v>1694.528228975167</v>
       </c>
       <c r="E30">
-        <v>-51.47086091881391</v>
+        <v>-34.09765451716373</v>
       </c>
       <c r="F30">
-        <v>486.4497792462055</v>
+        <v>503.8229856478557</v>
       </c>
       <c r="G30">
         <v>138.7</v>
@@ -3741,45 +3741,45 @@
         <v>115.22625</v>
       </c>
       <c r="M30">
-        <v>28.11679724043068</v>
+        <v>30.88434902021356</v>
       </c>
       <c r="N30">
-        <v>87.10945275956931</v>
+        <v>84.34190097978643</v>
       </c>
       <c r="O30">
-        <v>27.87502488306218</v>
+        <v>26.98940831353166</v>
       </c>
       <c r="P30">
-        <v>59.23442787650713</v>
+        <v>57.35249266625478</v>
       </c>
       <c r="Q30">
-        <v>116.0344278765071</v>
+        <v>114.1524926662548</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1389918543221394</v>
+        <v>0.1399722384427095</v>
       </c>
       <c r="T30">
-        <v>1.214602269006966</v>
+        <v>1.227379960641114</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.32</v>
       </c>
       <c r="W30">
-        <v>0.039304</v>
+        <v>0.041684</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.098128567584855</v>
+        <v>3.730894568138229</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1114686492943237</v>
+        <v>0.111191643476707</v>
       </c>
       <c r="C31">
-        <v>1329.405243327312</v>
+        <v>1319.210235126308</v>
       </c>
       <c r="D31">
-        <v>1694.528228975167</v>
+        <v>1701.706427175814</v>
       </c>
       <c r="E31">
-        <v>-34.09765451716379</v>
+        <v>-16.72444811551361</v>
       </c>
       <c r="F31">
-        <v>503.8229856478557</v>
+        <v>521.1961920495058</v>
       </c>
       <c r="G31">
         <v>138.7</v>
@@ -3823,28 +3823,28 @@
         <v>115.22625</v>
       </c>
       <c r="M31">
-        <v>30.88434902021355</v>
+        <v>31.94932657263471</v>
       </c>
       <c r="N31">
-        <v>84.34190097978644</v>
+        <v>83.27692342736529</v>
       </c>
       <c r="O31">
-        <v>26.98940831353166</v>
+        <v>26.64861549675689</v>
       </c>
       <c r="P31">
-        <v>57.35249266625478</v>
+        <v>56.6283079306084</v>
       </c>
       <c r="Q31">
-        <v>114.1524926662548</v>
+        <v>113.4283079306084</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1399722384427095</v>
+        <v>0.1409806335381529</v>
       </c>
       <c r="T31">
-        <v>1.227379960641114</v>
+        <v>1.240522729179095</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.73089456813823</v>
+        <v>3.606531415866955</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.111191643476707</v>
+        <v>0.1115048776590904</v>
       </c>
       <c r="C32">
-        <v>1319.210235126308</v>
+        <v>1293.724501308678</v>
       </c>
       <c r="D32">
-        <v>1701.706427175814</v>
+        <v>1693.593899759834</v>
       </c>
       <c r="E32">
-        <v>-16.72444811551361</v>
+        <v>0.6487582861366263</v>
       </c>
       <c r="F32">
-        <v>521.1961920495058</v>
+        <v>538.5693984511561</v>
       </c>
       <c r="G32">
         <v>138.7</v>
@@ -3905,45 +3905,45 @@
         <v>115.22625</v>
       </c>
       <c r="M32">
-        <v>31.94932657263471</v>
+        <v>34.5222984407191</v>
       </c>
       <c r="N32">
-        <v>83.27692342736529</v>
+        <v>80.70395155928088</v>
       </c>
       <c r="O32">
-        <v>26.64861549675689</v>
+        <v>25.82526449896988</v>
       </c>
       <c r="P32">
-        <v>56.6283079306084</v>
+        <v>54.87868706031099</v>
       </c>
       <c r="Q32">
-        <v>113.4283079306084</v>
+        <v>111.678687060311</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1409806335381529</v>
+        <v>0.1420182574769426</v>
       </c>
       <c r="T32">
-        <v>1.240522729179095</v>
+        <v>1.254046447529772</v>
       </c>
       <c r="U32">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.32</v>
       </c>
       <c r="W32">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.606531415866955</v>
+        <v>3.337734021327226</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1115048776590904</v>
+        <v>0.1112469118414737</v>
       </c>
       <c r="C33">
-        <v>1293.724501308678</v>
+        <v>1283.026771606683</v>
       </c>
       <c r="D33">
-        <v>1693.593899759834</v>
+        <v>1700.269376459489</v>
       </c>
       <c r="E33">
-        <v>0.6487582861366263</v>
+        <v>18.02196468778686</v>
       </c>
       <c r="F33">
-        <v>538.5693984511561</v>
+        <v>555.9426048528063</v>
       </c>
       <c r="G33">
         <v>138.7</v>
@@ -3987,28 +3987,28 @@
         <v>115.22625</v>
       </c>
       <c r="M33">
-        <v>34.5222984407191</v>
+        <v>35.63592097106488</v>
       </c>
       <c r="N33">
-        <v>80.70395155928088</v>
+        <v>79.59032902893512</v>
       </c>
       <c r="O33">
-        <v>25.82526449896988</v>
+        <v>25.46890528925924</v>
       </c>
       <c r="P33">
-        <v>54.87868706031099</v>
+        <v>54.12142373967588</v>
       </c>
       <c r="Q33">
-        <v>111.678687060311</v>
+        <v>110.9214237396759</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1420182574769426</v>
+        <v>0.1430863997668732</v>
       </c>
       <c r="T33">
-        <v>1.254046447529772</v>
+        <v>1.267967922302527</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.337734021327226</v>
+        <v>3.23342983316075</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1112469118414737</v>
+        <v>0.110988946023857</v>
       </c>
       <c r="C34">
-        <v>1283.026771606683</v>
+        <v>1272.381874322141</v>
       </c>
       <c r="D34">
-        <v>1700.269376459489</v>
+        <v>1706.997685576598</v>
       </c>
       <c r="E34">
-        <v>18.02196468778686</v>
+        <v>35.39517108943699</v>
       </c>
       <c r="F34">
-        <v>555.9426048528063</v>
+        <v>573.3158112544564</v>
       </c>
       <c r="G34">
         <v>138.7</v>
@@ -4069,28 +4069,28 @@
         <v>115.22625</v>
       </c>
       <c r="M34">
-        <v>35.63592097106488</v>
+        <v>36.74954350141066</v>
       </c>
       <c r="N34">
-        <v>79.59032902893512</v>
+        <v>78.47670649858932</v>
       </c>
       <c r="O34">
-        <v>25.46890528925924</v>
+        <v>25.11254607954858</v>
       </c>
       <c r="P34">
-        <v>54.12142373967588</v>
+        <v>53.36416041904074</v>
       </c>
       <c r="Q34">
-        <v>110.9214237396759</v>
+        <v>110.1641604190408</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1430863997668732</v>
+        <v>0.1441864269012792</v>
       </c>
       <c r="T34">
-        <v>1.267967922302527</v>
+        <v>1.282304963486409</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.23342983316075</v>
+        <v>3.135447110943757</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.110988946023857</v>
+        <v>0.1107309802062404</v>
       </c>
       <c r="C35">
-        <v>1272.381874322141</v>
+        <v>1261.790439152511</v>
       </c>
       <c r="D35">
-        <v>1706.997685576598</v>
+        <v>1713.779456808617</v>
       </c>
       <c r="E35">
-        <v>35.39517108943699</v>
+        <v>52.76837749108722</v>
       </c>
       <c r="F35">
-        <v>573.3158112544564</v>
+        <v>590.6890176561067</v>
       </c>
       <c r="G35">
         <v>138.7</v>
@@ -4151,28 +4151,28 @@
         <v>115.22625</v>
       </c>
       <c r="M35">
-        <v>36.74954350141066</v>
+        <v>37.86316603175644</v>
       </c>
       <c r="N35">
-        <v>78.47670649858932</v>
+        <v>77.36308396824356</v>
       </c>
       <c r="O35">
-        <v>25.11254607954858</v>
+        <v>24.75618686983794</v>
       </c>
       <c r="P35">
-        <v>53.36416041904074</v>
+        <v>52.60689709840562</v>
       </c>
       <c r="Q35">
-        <v>110.1641604190408</v>
+        <v>109.4068970984056</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1441864269012792</v>
+        <v>0.1453197881912733</v>
       </c>
       <c r="T35">
-        <v>1.282304963486409</v>
+        <v>1.297076460463742</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.135447110943757</v>
+        <v>3.043228078268941</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1107309802062404</v>
+        <v>0.1123294143886237</v>
       </c>
       <c r="C36">
-        <v>1261.790439152511</v>
+        <v>1203.242006875166</v>
       </c>
       <c r="D36">
-        <v>1713.779456808617</v>
+        <v>1672.604230932923</v>
       </c>
       <c r="E36">
-        <v>52.76837749108722</v>
+        <v>70.14158389273746</v>
       </c>
       <c r="F36">
-        <v>590.6890176561067</v>
+        <v>608.0622240577569</v>
       </c>
       <c r="G36">
         <v>138.7</v>
@@ -4233,45 +4233,45 @@
         <v>115.22625</v>
       </c>
       <c r="M36">
-        <v>37.86316603175644</v>
+        <v>43.71967390975273</v>
       </c>
       <c r="N36">
-        <v>77.36308396824356</v>
+        <v>71.50657609024726</v>
       </c>
       <c r="O36">
-        <v>24.75618686983794</v>
+        <v>22.88210434887912</v>
       </c>
       <c r="P36">
-        <v>52.60689709840562</v>
+        <v>48.62447174136814</v>
       </c>
       <c r="Q36">
-        <v>109.4068970984056</v>
+        <v>105.4244717413682</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1453197881912733</v>
+        <v>0.1464880221363442</v>
       </c>
       <c r="T36">
-        <v>1.297076460463742</v>
+        <v>1.312302465040378</v>
       </c>
       <c r="U36">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V36">
         <v>0.32</v>
       </c>
       <c r="W36">
-        <v>0.043588</v>
+        <v>0.048892</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.043228078268941</v>
+        <v>2.635569749167228</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1123294143886237</v>
+        <v>0.1121244885710071</v>
       </c>
       <c r="C37">
-        <v>1203.242006875166</v>
+        <v>1191.036722563198</v>
       </c>
       <c r="D37">
-        <v>1672.604230932923</v>
+        <v>1677.772153022605</v>
       </c>
       <c r="E37">
-        <v>70.14158389273746</v>
+        <v>87.51479029438769</v>
       </c>
       <c r="F37">
-        <v>608.0622240577569</v>
+        <v>625.4354304594071</v>
       </c>
       <c r="G37">
         <v>138.7</v>
@@ -4315,28 +4315,28 @@
         <v>115.22625</v>
       </c>
       <c r="M37">
-        <v>43.71967390975273</v>
+        <v>44.96880745003138</v>
       </c>
       <c r="N37">
-        <v>71.50657609024726</v>
+        <v>70.25744254996862</v>
       </c>
       <c r="O37">
-        <v>22.88210434887912</v>
+        <v>22.48238161598996</v>
       </c>
       <c r="P37">
-        <v>48.62447174136814</v>
+        <v>47.77506093397866</v>
       </c>
       <c r="Q37">
-        <v>105.4244717413682</v>
+        <v>104.5750609339787</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1464880221363442</v>
+        <v>0.1476927633921986</v>
       </c>
       <c r="T37">
-        <v>1.312302465040378</v>
+        <v>1.328004282260033</v>
       </c>
       <c r="U37">
         <v>0.07190000000000001</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.635569749167228</v>
+        <v>2.562359478357027</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1121244885710071</v>
+        <v>0.1129008027533904</v>
       </c>
       <c r="C38">
-        <v>1191.036722563199</v>
+        <v>1154.252745146093</v>
       </c>
       <c r="D38">
-        <v>1677.772153022606</v>
+        <v>1658.36138200715</v>
       </c>
       <c r="E38">
-        <v>87.51479029438758</v>
+        <v>104.8879966960378</v>
       </c>
       <c r="F38">
-        <v>625.435430459407</v>
+        <v>642.8086368610573</v>
       </c>
       <c r="G38">
         <v>138.7</v>
@@ -4397,45 +4397,45 @@
         <v>115.22625</v>
       </c>
       <c r="M38">
-        <v>44.96880745003137</v>
+        <v>48.72489467406815</v>
       </c>
       <c r="N38">
-        <v>70.25744254996863</v>
+        <v>66.50135532593185</v>
       </c>
       <c r="O38">
-        <v>22.48238161598996</v>
+        <v>21.28043370429819</v>
       </c>
       <c r="P38">
-        <v>47.77506093397866</v>
+        <v>45.22092162163366</v>
       </c>
       <c r="Q38">
-        <v>104.5750609339787</v>
+        <v>102.0209216216337</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1476927633921986</v>
+        <v>0.148935750402207</v>
       </c>
       <c r="T38">
-        <v>1.328004282260033</v>
+        <v>1.344204569867614</v>
       </c>
       <c r="U38">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V38">
         <v>0.32</v>
       </c>
       <c r="W38">
-        <v>0.048892</v>
+        <v>0.051544</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.562359478357028</v>
+        <v>2.364833228902278</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1129008027533904</v>
+        <v>0.1127223969357738</v>
       </c>
       <c r="C39">
-        <v>1154.252745146093</v>
+        <v>1141.30049991451</v>
       </c>
       <c r="D39">
-        <v>1658.36138200715</v>
+        <v>1662.782343177217</v>
       </c>
       <c r="E39">
-        <v>104.8879966960378</v>
+        <v>122.2612030976879</v>
       </c>
       <c r="F39">
-        <v>642.8086368610573</v>
+        <v>660.1818432627074</v>
       </c>
       <c r="G39">
         <v>138.7</v>
@@ -4479,28 +4479,28 @@
         <v>115.22625</v>
       </c>
       <c r="M39">
-        <v>48.72489467406815</v>
+        <v>50.04178371931322</v>
       </c>
       <c r="N39">
-        <v>66.50135532593185</v>
+        <v>65.18446628068676</v>
       </c>
       <c r="O39">
-        <v>21.28043370429819</v>
+        <v>20.85902920981976</v>
       </c>
       <c r="P39">
-        <v>45.22092162163366</v>
+        <v>44.325437070867</v>
       </c>
       <c r="Q39">
-        <v>102.0209216216337</v>
+        <v>101.125437070867</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.148935750402207</v>
+        <v>0.150218833767377</v>
       </c>
       <c r="T39">
-        <v>1.344204569867614</v>
+        <v>1.36092744739802</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.364833228902278</v>
+        <v>2.302600775510113</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1127223969357738</v>
+        <v>0.1125439911181571</v>
       </c>
       <c r="C40">
-        <v>1141.30049991451</v>
+        <v>1128.371889026003</v>
       </c>
       <c r="D40">
-        <v>1662.782343177217</v>
+        <v>1667.226938690361</v>
       </c>
       <c r="E40">
-        <v>122.2612030976879</v>
+        <v>139.6344094993382</v>
       </c>
       <c r="F40">
-        <v>660.1818432627074</v>
+        <v>677.5550496643576</v>
       </c>
       <c r="G40">
         <v>138.7</v>
@@ -4561,28 +4561,28 @@
         <v>115.22625</v>
       </c>
       <c r="M40">
-        <v>50.04178371931322</v>
+        <v>51.35867276455831</v>
       </c>
       <c r="N40">
-        <v>65.18446628068676</v>
+        <v>63.86757723544168</v>
       </c>
       <c r="O40">
-        <v>20.85902920981976</v>
+        <v>20.43762471534134</v>
       </c>
       <c r="P40">
-        <v>44.325437070867</v>
+        <v>43.42995252010034</v>
       </c>
       <c r="Q40">
-        <v>101.125437070867</v>
+        <v>100.2299525201004</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.150218833767377</v>
+        <v>0.1515439854396018</v>
       </c>
       <c r="T40">
-        <v>1.36092744739802</v>
+        <v>1.378198615994997</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.302600775510113</v>
+        <v>2.243559729984213</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1125439911181571</v>
+        <v>0.1123655853005404</v>
       </c>
       <c r="C41">
-        <v>1128.371889026003</v>
+        <v>1115.467102511397</v>
       </c>
       <c r="D41">
-        <v>1667.226938690361</v>
+        <v>1671.695358577404</v>
       </c>
       <c r="E41">
-        <v>139.6344094993382</v>
+        <v>157.0076159009884</v>
       </c>
       <c r="F41">
-        <v>677.5550496643576</v>
+        <v>694.9282560660079</v>
       </c>
       <c r="G41">
         <v>138.7</v>
@@ -4643,28 +4643,28 @@
         <v>115.22625</v>
       </c>
       <c r="M41">
-        <v>51.35867276455831</v>
+        <v>52.6755618098034</v>
       </c>
       <c r="N41">
-        <v>63.86757723544168</v>
+        <v>62.5506881901966</v>
       </c>
       <c r="O41">
-        <v>20.43762471534134</v>
+        <v>20.01622022086291</v>
       </c>
       <c r="P41">
-        <v>43.42995252010034</v>
+        <v>42.53446796933368</v>
       </c>
       <c r="Q41">
-        <v>100.2299525201004</v>
+        <v>99.3344679693337</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1515439854396018</v>
+        <v>0.152913308834234</v>
       </c>
       <c r="T41">
-        <v>1.378198615994997</v>
+        <v>1.396045490211873</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.243559729984213</v>
+        <v>2.187470736734608</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1123655853005404</v>
+        <v>0.1121871794829238</v>
       </c>
       <c r="C42">
-        <v>1115.467102511397</v>
+        <v>1102.58633244423</v>
       </c>
       <c r="D42">
-        <v>1671.695358577404</v>
+        <v>1676.187794911888</v>
       </c>
       <c r="E42">
-        <v>157.0076159009884</v>
+        <v>174.3808223026386</v>
       </c>
       <c r="F42">
-        <v>694.9282560660079</v>
+        <v>712.3014624676581</v>
       </c>
       <c r="G42">
         <v>138.7</v>
@@ -4725,28 +4725,28 @@
         <v>115.22625</v>
       </c>
       <c r="M42">
-        <v>52.6755618098034</v>
+        <v>53.99245085504849</v>
       </c>
       <c r="N42">
-        <v>62.5506881901966</v>
+        <v>61.2337991449515</v>
       </c>
       <c r="O42">
-        <v>20.01622022086291</v>
+        <v>19.59481572638448</v>
       </c>
       <c r="P42">
-        <v>42.53446796933368</v>
+        <v>41.63898341856702</v>
       </c>
       <c r="Q42">
-        <v>99.3344679693337</v>
+        <v>98.43898341856703</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.152913308834234</v>
+        <v>0.1543290499710572</v>
       </c>
       <c r="T42">
-        <v>1.396045490211873</v>
+        <v>1.414497343215762</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.187470736734608</v>
+        <v>2.134117791936202</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1121871794829238</v>
+        <v>0.1120087736653071</v>
       </c>
       <c r="C43">
-        <v>1102.58633244423</v>
+        <v>1089.729772968289</v>
       </c>
       <c r="D43">
-        <v>1676.187794911888</v>
+        <v>1680.704441837597</v>
       </c>
       <c r="E43">
-        <v>174.3808223026386</v>
+        <v>191.7540287042888</v>
       </c>
       <c r="F43">
-        <v>712.3014624676581</v>
+        <v>729.6746688693082</v>
       </c>
       <c r="G43">
         <v>138.7</v>
@@ -4807,28 +4807,28 @@
         <v>115.22625</v>
       </c>
       <c r="M43">
-        <v>53.99245085504849</v>
+        <v>55.30933990029357</v>
       </c>
       <c r="N43">
-        <v>61.2337991449515</v>
+        <v>59.91691009970643</v>
       </c>
       <c r="O43">
-        <v>19.59481572638448</v>
+        <v>19.17341123190606</v>
       </c>
       <c r="P43">
-        <v>41.63898341856702</v>
+        <v>40.74349886780037</v>
       </c>
       <c r="Q43">
-        <v>98.43898341856703</v>
+        <v>97.54349886780038</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1543290499710572</v>
+        <v>0.1557936097677709</v>
       </c>
       <c r="T43">
-        <v>1.414497343215762</v>
+        <v>1.433585467012888</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.134117791936202</v>
+        <v>2.083305463556769</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1120087736653071</v>
+        <v>0.1118303678476905</v>
       </c>
       <c r="C44">
-        <v>1089.729772968288</v>
+        <v>1076.897620325563</v>
       </c>
       <c r="D44">
-        <v>1680.704441837596</v>
+        <v>1685.245495596521</v>
       </c>
       <c r="E44">
-        <v>191.7540287042888</v>
+        <v>209.1272351059389</v>
       </c>
       <c r="F44">
-        <v>729.6746688693082</v>
+        <v>747.0478752709583</v>
       </c>
       <c r="G44">
         <v>138.7</v>
@@ -4889,28 +4889,28 @@
         <v>115.22625</v>
       </c>
       <c r="M44">
-        <v>55.30933990029357</v>
+        <v>56.62622894553865</v>
       </c>
       <c r="N44">
-        <v>59.91691009970643</v>
+        <v>58.60002105446134</v>
       </c>
       <c r="O44">
-        <v>19.17341123190606</v>
+        <v>18.75200673742763</v>
       </c>
       <c r="P44">
-        <v>40.74349886780037</v>
+        <v>39.84801431703372</v>
       </c>
       <c r="Q44">
-        <v>97.54349886780038</v>
+        <v>96.64801431703373</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1557936097677709</v>
+        <v>0.1573095576275271</v>
       </c>
       <c r="T44">
-        <v>1.433585467012888</v>
+        <v>1.453343349539739</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.083305463556769</v>
+        <v>2.034856499288007</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1118303678476905</v>
+        <v>0.1159006020300738</v>
       </c>
       <c r="C45">
-        <v>1076.897620325563</v>
+        <v>961.6744151615371</v>
       </c>
       <c r="D45">
-        <v>1685.245495596521</v>
+        <v>1587.395496834146</v>
       </c>
       <c r="E45">
-        <v>209.1272351059389</v>
+        <v>226.5004415075891</v>
       </c>
       <c r="F45">
-        <v>747.0478752709583</v>
+        <v>764.4210816726086</v>
       </c>
       <c r="G45">
         <v>138.7</v>
@@ -4971,45 +4971,45 @@
         <v>115.22625</v>
       </c>
       <c r="M45">
-        <v>56.62622894553865</v>
+        <v>68.79789735053477</v>
       </c>
       <c r="N45">
-        <v>58.60002105446134</v>
+        <v>46.42835264946522</v>
       </c>
       <c r="O45">
-        <v>18.75200673742763</v>
+        <v>14.85707284782887</v>
       </c>
       <c r="P45">
-        <v>39.84801431703372</v>
+        <v>31.57127980163635</v>
       </c>
       <c r="Q45">
-        <v>96.64801431703373</v>
+        <v>88.37127980163636</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1573095576275271</v>
+        <v>0.1588796464822746</v>
       </c>
       <c r="T45">
-        <v>1.453343349539739</v>
+        <v>1.473806870728262</v>
       </c>
       <c r="U45">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V45">
         <v>0.32</v>
       </c>
       <c r="W45">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.034856499288007</v>
+        <v>1.674851331762457</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1159006020300738</v>
+        <v>0.1158187562124571</v>
       </c>
       <c r="C46">
-        <v>961.6744151615371</v>
+        <v>946.1567356122238</v>
       </c>
       <c r="D46">
-        <v>1587.395496834146</v>
+        <v>1589.251023686483</v>
       </c>
       <c r="E46">
-        <v>226.5004415075891</v>
+        <v>243.8736479092394</v>
       </c>
       <c r="F46">
-        <v>764.4210816726086</v>
+        <v>781.7942880742588</v>
       </c>
       <c r="G46">
         <v>138.7</v>
@@ -5053,28 +5053,28 @@
         <v>115.22625</v>
       </c>
       <c r="M46">
-        <v>68.79789735053477</v>
+        <v>70.36148592668329</v>
       </c>
       <c r="N46">
-        <v>46.42835264946522</v>
+        <v>44.86476407331671</v>
       </c>
       <c r="O46">
-        <v>14.85707284782887</v>
+        <v>14.35672450346135</v>
       </c>
       <c r="P46">
-        <v>31.57127980163635</v>
+        <v>30.50803956985536</v>
       </c>
       <c r="Q46">
-        <v>88.37127980163636</v>
+        <v>87.30803956985537</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1588796464822746</v>
+        <v>0.1605068294771947</v>
       </c>
       <c r="T46">
-        <v>1.473806870728262</v>
+        <v>1.495014519960004</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.674851331762457</v>
+        <v>1.637632413278847</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1158187562124571</v>
+        <v>0.1157369103948405</v>
       </c>
       <c r="C47">
-        <v>946.1567356122238</v>
+        <v>930.6433990374985</v>
       </c>
       <c r="D47">
-        <v>1589.251023686483</v>
+        <v>1591.110893513408</v>
       </c>
       <c r="E47">
-        <v>243.8736479092394</v>
+        <v>261.2468543108896</v>
       </c>
       <c r="F47">
-        <v>781.7942880742588</v>
+        <v>799.1674944759091</v>
       </c>
       <c r="G47">
         <v>138.7</v>
@@ -5135,28 +5135,28 @@
         <v>115.22625</v>
       </c>
       <c r="M47">
-        <v>70.36148592668329</v>
+        <v>71.92507450283181</v>
       </c>
       <c r="N47">
-        <v>44.86476407331671</v>
+        <v>43.30117549716819</v>
       </c>
       <c r="O47">
-        <v>14.35672450346135</v>
+        <v>13.85637615909382</v>
       </c>
       <c r="P47">
-        <v>30.50803956985536</v>
+        <v>29.44479933807437</v>
       </c>
       <c r="Q47">
-        <v>87.30803956985537</v>
+        <v>86.24479933807439</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1605068294771947</v>
+        <v>0.1621942785089638</v>
       </c>
       <c r="T47">
-        <v>1.495014519960004</v>
+        <v>1.517007637681811</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.637632413278847</v>
+        <v>1.60203170864235</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1157369103948405</v>
+        <v>0.1156550645772238</v>
       </c>
       <c r="C48">
-        <v>930.6433990374985</v>
+        <v>915.1344207027256</v>
       </c>
       <c r="D48">
-        <v>1591.110893513408</v>
+        <v>1592.975121580285</v>
       </c>
       <c r="E48">
-        <v>261.2468543108896</v>
+        <v>278.6200607125398</v>
       </c>
       <c r="F48">
-        <v>799.1674944759091</v>
+        <v>816.5407008775593</v>
       </c>
       <c r="G48">
         <v>138.7</v>
@@ -5217,28 +5217,28 @@
         <v>115.22625</v>
       </c>
       <c r="M48">
-        <v>71.92507450283181</v>
+        <v>73.48866307898034</v>
       </c>
       <c r="N48">
-        <v>43.30117549716819</v>
+        <v>41.73758692101966</v>
       </c>
       <c r="O48">
-        <v>13.85637615909382</v>
+        <v>13.35602781472629</v>
       </c>
       <c r="P48">
-        <v>29.44479933807437</v>
+        <v>28.38155910629337</v>
       </c>
       <c r="Q48">
-        <v>86.24479933807439</v>
+        <v>85.18155910629338</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1621942785089638</v>
+        <v>0.1639454048626864</v>
       </c>
       <c r="T48">
-        <v>1.517007637681811</v>
+        <v>1.539830684374252</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.60203170864235</v>
+        <v>1.567945927607406</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1156550645772238</v>
+        <v>0.1155732187596071</v>
       </c>
       <c r="C49">
-        <v>915.1344207027256</v>
+        <v>899.6298159448944</v>
       </c>
       <c r="D49">
-        <v>1592.975121580285</v>
+        <v>1594.843723224104</v>
       </c>
       <c r="E49">
-        <v>278.6200607125398</v>
+        <v>295.99326711419</v>
       </c>
       <c r="F49">
-        <v>816.5407008775593</v>
+        <v>833.9139072792094</v>
       </c>
       <c r="G49">
         <v>138.7</v>
@@ -5299,28 +5299,28 @@
         <v>115.22625</v>
       </c>
       <c r="M49">
-        <v>73.48866307898034</v>
+        <v>75.05225165512884</v>
       </c>
       <c r="N49">
-        <v>41.73758692101966</v>
+        <v>40.17399834487115</v>
       </c>
       <c r="O49">
-        <v>13.35602781472629</v>
+        <v>12.85567947035877</v>
       </c>
       <c r="P49">
-        <v>28.38155910629337</v>
+        <v>27.31831887451238</v>
       </c>
       <c r="Q49">
-        <v>85.18155910629338</v>
+        <v>84.1183188745124</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1639454048626864</v>
+        <v>0.1657638822300137</v>
       </c>
       <c r="T49">
-        <v>1.539830684374252</v>
+        <v>1.563531540554864</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.567945927607406</v>
+        <v>1.535280387448919</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1155732187596071</v>
+        <v>0.1154913729419905</v>
       </c>
       <c r="C50">
-        <v>899.6298159448945</v>
+        <v>884.1296001730419</v>
       </c>
       <c r="D50">
-        <v>1594.843723224104</v>
+        <v>1596.716713853901</v>
       </c>
       <c r="E50">
-        <v>295.9932671141898</v>
+        <v>313.3664735158401</v>
       </c>
       <c r="F50">
-        <v>833.9139072792093</v>
+        <v>851.2871136808595</v>
       </c>
       <c r="G50">
         <v>138.7</v>
@@ -5381,28 +5381,28 @@
         <v>115.22625</v>
       </c>
       <c r="M50">
-        <v>75.05225165512883</v>
+        <v>76.61584023127736</v>
       </c>
       <c r="N50">
-        <v>40.17399834487117</v>
+        <v>38.61040976872263</v>
       </c>
       <c r="O50">
-        <v>12.85567947035877</v>
+        <v>12.35533112599124</v>
       </c>
       <c r="P50">
-        <v>27.31831887451239</v>
+        <v>26.25507864273139</v>
       </c>
       <c r="Q50">
-        <v>84.1183188745124</v>
+        <v>83.0550786427314</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1657638822300137</v>
+        <v>0.1676536724352754</v>
       </c>
       <c r="T50">
-        <v>1.563531540554864</v>
+        <v>1.588161842075892</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.535280387448919</v>
+        <v>1.503948134643839</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1154913729419905</v>
+        <v>0.1381226083348729</v>
       </c>
       <c r="C51">
-        <v>884.1296001730419</v>
+        <v>475.3498633589716</v>
       </c>
       <c r="D51">
-        <v>1596.716713853901</v>
+        <v>1205.310183441481</v>
       </c>
       <c r="E51">
-        <v>313.3664735158401</v>
+        <v>330.7396799174903</v>
       </c>
       <c r="F51">
-        <v>851.2871136808595</v>
+        <v>868.6603200825098</v>
       </c>
       <c r="G51">
         <v>138.7</v>
@@ -5463,45 +5463,45 @@
         <v>115.22625</v>
       </c>
       <c r="M51">
-        <v>76.61584023127736</v>
+        <v>127.5193349881124</v>
       </c>
       <c r="N51">
-        <v>38.61040976872263</v>
+        <v>-12.29308498811245</v>
       </c>
       <c r="O51">
-        <v>12.35533112599124</v>
+        <v>-3.933787196195985</v>
       </c>
       <c r="P51">
-        <v>26.25507864273139</v>
+        <v>-8.359297791916468</v>
       </c>
       <c r="Q51">
-        <v>83.0550786427314</v>
+        <v>48.44070220808354</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1676536724352754</v>
+        <v>0.1718926488219335</v>
       </c>
       <c r="T51">
-        <v>1.588161842075892</v>
+        <v>1.643409914720786</v>
       </c>
       <c r="U51">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.32</v>
+        <v>0.2891514451783904</v>
       </c>
       <c r="W51">
-        <v>0.06119999999999999</v>
+        <v>0.1043525678478123</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.503948134643839</v>
+        <v>0.90359826618247</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1381226083348729</v>
+        <v>0.1391326083348729</v>
       </c>
       <c r="C52">
-        <v>475.3498633589716</v>
+        <v>444.9333775826782</v>
       </c>
       <c r="D52">
-        <v>1205.310183441481</v>
+        <v>1192.266904066838</v>
       </c>
       <c r="E52">
-        <v>330.7396799174903</v>
+        <v>348.1128863191406</v>
       </c>
       <c r="F52">
-        <v>868.6603200825098</v>
+        <v>886.03352648416</v>
       </c>
       <c r="G52">
         <v>138.7</v>
@@ -5545,37 +5545,37 @@
         <v>115.22625</v>
       </c>
       <c r="M52">
-        <v>127.5193349881124</v>
+        <v>130.0697216878747</v>
       </c>
       <c r="N52">
-        <v>-12.29308498811245</v>
+        <v>-14.84347168787471</v>
       </c>
       <c r="O52">
-        <v>-3.933787196195985</v>
+        <v>-4.749910940119908</v>
       </c>
       <c r="P52">
-        <v>-8.359297791916468</v>
+        <v>-10.0935607477548</v>
       </c>
       <c r="Q52">
-        <v>48.44070220808354</v>
+        <v>46.7064392522452</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1718926488219335</v>
+        <v>0.1744659681856465</v>
       </c>
       <c r="T52">
-        <v>1.643409914720786</v>
+        <v>1.67694889257223</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2891514451783904</v>
+        <v>0.283481808998422</v>
       </c>
       <c r="W52">
-        <v>0.1043525678478123</v>
+        <v>0.1051848704390317</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.90359826618247</v>
+        <v>0.8858806531200686</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1391326083348729</v>
+        <v>0.1401426083348729</v>
       </c>
       <c r="C53">
-        <v>444.9333775826782</v>
+        <v>414.7961656657981</v>
       </c>
       <c r="D53">
-        <v>1192.266904066838</v>
+        <v>1179.502898551608</v>
       </c>
       <c r="E53">
-        <v>348.1128863191406</v>
+        <v>365.4860927207908</v>
       </c>
       <c r="F53">
-        <v>886.03352648416</v>
+        <v>903.4067328858102</v>
       </c>
       <c r="G53">
         <v>138.7</v>
@@ -5627,37 +5627,37 @@
         <v>115.22625</v>
       </c>
       <c r="M53">
-        <v>130.0697216878747</v>
+        <v>132.6201083876369</v>
       </c>
       <c r="N53">
-        <v>-14.84347168787471</v>
+        <v>-17.39385838763695</v>
       </c>
       <c r="O53">
-        <v>-4.749910940119908</v>
+        <v>-5.566034684043825</v>
       </c>
       <c r="P53">
-        <v>-10.0935607477548</v>
+        <v>-11.82782370359313</v>
       </c>
       <c r="Q53">
-        <v>46.7064392522452</v>
+        <v>44.97217629640689</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1744659681856465</v>
+        <v>0.1771465091895141</v>
       </c>
       <c r="T53">
-        <v>1.67694889257223</v>
+        <v>1.711885327834152</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.283481808998422</v>
+        <v>0.2780302357484523</v>
       </c>
       <c r="W53">
-        <v>0.1051848704390317</v>
+        <v>0.1059851613921272</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8858806531200686</v>
+        <v>0.8688444867139135</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1401426083348729</v>
+        <v>0.1411526083348729</v>
       </c>
       <c r="C54">
-        <v>414.7961656657981</v>
+        <v>384.9293531809944</v>
       </c>
       <c r="D54">
-        <v>1179.502898551608</v>
+        <v>1167.009292468455</v>
       </c>
       <c r="E54">
-        <v>365.4860927207908</v>
+        <v>382.8592991224409</v>
       </c>
       <c r="F54">
-        <v>903.4067328858102</v>
+        <v>920.7799392874604</v>
       </c>
       <c r="G54">
         <v>138.7</v>
@@ -5709,37 +5709,37 @@
         <v>115.22625</v>
       </c>
       <c r="M54">
-        <v>132.6201083876369</v>
+        <v>135.1704950873992</v>
       </c>
       <c r="N54">
-        <v>-17.39385838763695</v>
+        <v>-19.9442450873992</v>
       </c>
       <c r="O54">
-        <v>-5.566034684043825</v>
+        <v>-6.382158427967743</v>
       </c>
       <c r="P54">
-        <v>-11.82782370359313</v>
+        <v>-13.56208665943145</v>
       </c>
       <c r="Q54">
-        <v>44.97217629640689</v>
+        <v>43.23791334056855</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1771465091895141</v>
+        <v>0.1799411157680144</v>
       </c>
       <c r="T54">
-        <v>1.711885327834152</v>
+        <v>1.74830841991573</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2780302357484523</v>
+        <v>0.2727843822437646</v>
       </c>
       <c r="W54">
-        <v>0.1059851613921272</v>
+        <v>0.1067552526866154</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8688444867139135</v>
+        <v>0.8524511945117642</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1411526083348729</v>
+        <v>0.1421626083348729</v>
       </c>
       <c r="C55">
-        <v>384.9293531809944</v>
+        <v>355.3244377610796</v>
       </c>
       <c r="D55">
-        <v>1167.009292468455</v>
+        <v>1154.77758345019</v>
       </c>
       <c r="E55">
-        <v>382.8592991224409</v>
+        <v>400.2325055240912</v>
       </c>
       <c r="F55">
-        <v>920.7799392874604</v>
+        <v>938.1531456891106</v>
       </c>
       <c r="G55">
         <v>138.7</v>
@@ -5791,37 +5791,37 @@
         <v>115.22625</v>
       </c>
       <c r="M55">
-        <v>135.1704950873992</v>
+        <v>137.7208817871615</v>
       </c>
       <c r="N55">
-        <v>-19.9442450873992</v>
+        <v>-22.49463178716147</v>
       </c>
       <c r="O55">
-        <v>-6.382158427967743</v>
+        <v>-7.19828217189167</v>
       </c>
       <c r="P55">
-        <v>-13.56208665943145</v>
+        <v>-15.2963496152698</v>
       </c>
       <c r="Q55">
-        <v>43.23791334056855</v>
+        <v>41.50365038473021</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1799411157680144</v>
+        <v>0.1828572269803626</v>
       </c>
       <c r="T55">
-        <v>1.74830841991573</v>
+        <v>1.786315124696506</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.2727843822437646</v>
+        <v>0.2677328196096207</v>
       </c>
       <c r="W55">
-        <v>0.1067552526866154</v>
+        <v>0.1074968220813077</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8524511945117642</v>
+        <v>0.8366650612800648</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1421626083348729</v>
+        <v>0.1431726083348729</v>
       </c>
       <c r="C56">
-        <v>355.3244377610796</v>
+        <v>325.9732698029968</v>
       </c>
       <c r="D56">
-        <v>1154.77758345019</v>
+        <v>1142.799621893758</v>
       </c>
       <c r="E56">
-        <v>400.2325055240912</v>
+        <v>417.6057119257414</v>
       </c>
       <c r="F56">
-        <v>938.1531456891106</v>
+        <v>955.5263520907608</v>
       </c>
       <c r="G56">
         <v>138.7</v>
@@ -5873,37 +5873,37 @@
         <v>115.22625</v>
       </c>
       <c r="M56">
-        <v>137.7208817871615</v>
+        <v>140.2712684869237</v>
       </c>
       <c r="N56">
-        <v>-22.49463178716147</v>
+        <v>-25.04501848692371</v>
       </c>
       <c r="O56">
-        <v>-7.19828217189167</v>
+        <v>-8.014405915815587</v>
       </c>
       <c r="P56">
-        <v>-15.2963496152698</v>
+        <v>-17.03061257110812</v>
       </c>
       <c r="Q56">
-        <v>41.50365038473021</v>
+        <v>39.76938742889189</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1828572269803626</v>
+        <v>0.1859029431354817</v>
       </c>
       <c r="T56">
-        <v>1.786315124696506</v>
+        <v>1.826011016356429</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2677328196096207</v>
+        <v>0.2628649501621731</v>
       </c>
       <c r="W56">
-        <v>0.1074968220813077</v>
+        <v>0.108211425316193</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8366650612800648</v>
+        <v>0.8214529692567909</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1431726083348729</v>
+        <v>0.1441826083348729</v>
       </c>
       <c r="C57">
-        <v>325.9732698029968</v>
+        <v>296.8680343603602</v>
       </c>
       <c r="D57">
-        <v>1142.799621893758</v>
+        <v>1131.067592852771</v>
       </c>
       <c r="E57">
-        <v>417.6057119257414</v>
+        <v>434.9789183273916</v>
       </c>
       <c r="F57">
-        <v>955.5263520907608</v>
+        <v>972.8995584924111</v>
       </c>
       <c r="G57">
         <v>138.7</v>
@@ -5955,37 +5955,37 @@
         <v>115.22625</v>
       </c>
       <c r="M57">
-        <v>140.2712684869237</v>
+        <v>142.821655186686</v>
       </c>
       <c r="N57">
-        <v>-25.04501848692371</v>
+        <v>-27.59540518668598</v>
       </c>
       <c r="O57">
-        <v>-8.014405915815587</v>
+        <v>-8.830529659739513</v>
       </c>
       <c r="P57">
-        <v>-17.03061257110812</v>
+        <v>-18.76487552694647</v>
       </c>
       <c r="Q57">
-        <v>39.76938742889189</v>
+        <v>38.03512447305354</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1859029431354817</v>
+        <v>0.1890871009340154</v>
       </c>
       <c r="T57">
-        <v>1.826011016356429</v>
+        <v>1.867511266728166</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2628649501621731</v>
+        <v>0.2581709331949913</v>
       </c>
       <c r="W57">
-        <v>0.108211425316193</v>
+        <v>0.1089005070069753</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8214529692567909</v>
+        <v>0.806784166234348</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1441826083348729</v>
+        <v>0.178838129520575</v>
       </c>
       <c r="C58">
-        <v>296.8680343603602</v>
+        <v>-15.14053009860606</v>
       </c>
       <c r="D58">
-        <v>1131.067592852771</v>
+        <v>836.4322347954551</v>
       </c>
       <c r="E58">
-        <v>434.9789183273916</v>
+        <v>452.3521247290417</v>
       </c>
       <c r="F58">
-        <v>972.8995584924111</v>
+        <v>990.2727648940612</v>
       </c>
       <c r="G58">
         <v>138.7</v>
@@ -6037,45 +6037,45 @@
         <v>115.22625</v>
       </c>
       <c r="M58">
-        <v>142.821655186686</v>
+        <v>198.8467711907275</v>
       </c>
       <c r="N58">
-        <v>-27.59540518668598</v>
+        <v>-83.62052119072749</v>
       </c>
       <c r="O58">
-        <v>-8.830529659739513</v>
+        <v>-26.7585667810328</v>
       </c>
       <c r="P58">
-        <v>-18.76487552694647</v>
+        <v>-56.86195440969469</v>
       </c>
       <c r="Q58">
-        <v>38.03512447305354</v>
+        <v>-0.06195440969467825</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1890871009340154</v>
+        <v>0.1990833618527182</v>
       </c>
       <c r="T58">
-        <v>1.867511266728166</v>
+        <v>1.997796056978955</v>
       </c>
       <c r="U58">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.2581709331949913</v>
+        <v>0.1854312231433377</v>
       </c>
       <c r="W58">
-        <v>0.1089005070069753</v>
+        <v>0.1635654103928178</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.806784166234348</v>
+        <v>0.5794725723229303</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.178838129520575</v>
+        <v>0.180388129520575</v>
       </c>
       <c r="C59">
-        <v>-15.14053009860606</v>
+        <v>-42.14660656503247</v>
       </c>
       <c r="D59">
-        <v>836.4322347954551</v>
+        <v>826.799364730679</v>
       </c>
       <c r="E59">
-        <v>452.3521247290417</v>
+        <v>469.725331130692</v>
       </c>
       <c r="F59">
-        <v>990.2727648940612</v>
+        <v>1007.645971295711</v>
       </c>
       <c r="G59">
         <v>138.7</v>
@@ -6119,37 +6119,37 @@
         <v>115.22625</v>
       </c>
       <c r="M59">
-        <v>198.8467711907275</v>
+        <v>202.3353110361789</v>
       </c>
       <c r="N59">
-        <v>-83.62052119072749</v>
+        <v>-87.10906103617887</v>
       </c>
       <c r="O59">
-        <v>-26.7585667810328</v>
+        <v>-27.87489953157724</v>
       </c>
       <c r="P59">
-        <v>-56.86195440969469</v>
+        <v>-59.23416150460163</v>
       </c>
       <c r="Q59">
-        <v>-0.06195440969467825</v>
+        <v>-2.434161504601619</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1990833618527182</v>
+        <v>0.2027329657063543</v>
       </c>
       <c r="T59">
-        <v>1.997796056978955</v>
+        <v>2.045362629764168</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1854312231433377</v>
+        <v>0.1822341330891422</v>
       </c>
       <c r="W59">
-        <v>0.1635654103928178</v>
+        <v>0.1642073860757003</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5794725723229303</v>
+        <v>0.5694816659035693</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.180388129520575</v>
+        <v>0.1819381295205749</v>
       </c>
       <c r="C60">
-        <v>-42.14660656503236</v>
+        <v>-68.93333304254679</v>
       </c>
       <c r="D60">
-        <v>826.799364730679</v>
+        <v>817.3858446548147</v>
       </c>
       <c r="E60">
-        <v>469.7253311306919</v>
+        <v>487.0985375323421</v>
       </c>
       <c r="F60">
-        <v>1007.645971295711</v>
+        <v>1025.019177697362</v>
       </c>
       <c r="G60">
         <v>138.7</v>
@@ -6201,37 +6201,37 @@
         <v>115.22625</v>
       </c>
       <c r="M60">
-        <v>202.3353110361788</v>
+        <v>205.8238508816302</v>
       </c>
       <c r="N60">
-        <v>-87.10906103617884</v>
+        <v>-90.5976008816302</v>
       </c>
       <c r="O60">
-        <v>-27.87489953157723</v>
+        <v>-28.99123228212166</v>
       </c>
       <c r="P60">
-        <v>-59.23416150460162</v>
+        <v>-61.60636859950854</v>
       </c>
       <c r="Q60">
-        <v>-2.434161504601605</v>
+        <v>-4.806368599508524</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2027329657063543</v>
+        <v>0.2065605990162653</v>
       </c>
       <c r="T60">
-        <v>2.045362629764168</v>
+        <v>2.09524952317305</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1822341330891422</v>
+        <v>0.1791454189689873</v>
       </c>
       <c r="W60">
-        <v>0.1642073860757003</v>
+        <v>0.1648275998710274</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5694816659035694</v>
+        <v>0.5598294342780852</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1819381295205749</v>
+        <v>0.1834881295205749</v>
       </c>
       <c r="C61">
-        <v>-68.93333304254679</v>
+        <v>-95.50811741338271</v>
       </c>
       <c r="D61">
-        <v>817.3858446548147</v>
+        <v>808.1842666856289</v>
       </c>
       <c r="E61">
-        <v>487.0985375323421</v>
+        <v>504.4717439339922</v>
       </c>
       <c r="F61">
-        <v>1025.019177697362</v>
+        <v>1042.392384099012</v>
       </c>
       <c r="G61">
         <v>138.7</v>
@@ -6283,37 +6283,37 @@
         <v>115.22625</v>
       </c>
       <c r="M61">
-        <v>205.8238508816302</v>
+        <v>209.3123907270815</v>
       </c>
       <c r="N61">
-        <v>-90.5976008816302</v>
+        <v>-94.08614072708156</v>
       </c>
       <c r="O61">
-        <v>-28.99123228212166</v>
+        <v>-30.1075650326661</v>
       </c>
       <c r="P61">
-        <v>-61.60636859950854</v>
+        <v>-63.97857569441545</v>
       </c>
       <c r="Q61">
-        <v>-4.806368599508524</v>
+        <v>-7.178575694415443</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2065605990162653</v>
+        <v>0.210579613991672</v>
       </c>
       <c r="T61">
-        <v>2.09524952317305</v>
+        <v>2.147630761252376</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1791454189689873</v>
+        <v>0.1761596619861708</v>
       </c>
       <c r="W61">
-        <v>0.1648275998710274</v>
+        <v>0.1654271398731769</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5598294342780852</v>
+        <v>0.5504989437067838</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1834881295205749</v>
+        <v>0.1850381295205749</v>
       </c>
       <c r="C62">
-        <v>-95.50811741338271</v>
+        <v>-121.8780377013513</v>
       </c>
       <c r="D62">
-        <v>808.1842666856289</v>
+        <v>799.1875527993105</v>
       </c>
       <c r="E62">
-        <v>504.4717439339922</v>
+        <v>521.8449503356424</v>
       </c>
       <c r="F62">
-        <v>1042.392384099012</v>
+        <v>1059.765590500662</v>
       </c>
       <c r="G62">
         <v>138.7</v>
@@ -6365,37 +6365,37 @@
         <v>115.22625</v>
       </c>
       <c r="M62">
-        <v>209.3123907270815</v>
+        <v>212.8009305725329</v>
       </c>
       <c r="N62">
-        <v>-94.08614072708156</v>
+        <v>-97.57468057253291</v>
       </c>
       <c r="O62">
-        <v>-30.1075650326661</v>
+        <v>-31.22389778321053</v>
       </c>
       <c r="P62">
-        <v>-63.97857569441545</v>
+        <v>-66.35078278932238</v>
       </c>
       <c r="Q62">
-        <v>-7.178575694415443</v>
+        <v>-9.550782789322369</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.210579613991672</v>
+        <v>0.2148047322991508</v>
       </c>
       <c r="T62">
-        <v>2.147630761252376</v>
+        <v>2.202698216669104</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1761596619861708</v>
+        <v>0.1732717986749221</v>
       </c>
       <c r="W62">
-        <v>0.1654271398731769</v>
+        <v>0.1660070228260756</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5504989437067838</v>
+        <v>0.5414743708591316</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1850381295205749</v>
+        <v>0.186588129520575</v>
       </c>
       <c r="C63">
-        <v>-121.8780377013513</v>
+        <v>-148.04986022964</v>
       </c>
       <c r="D63">
-        <v>799.1875527993105</v>
+        <v>790.3889366726722</v>
       </c>
       <c r="E63">
-        <v>521.8449503356424</v>
+        <v>539.2181567372927</v>
       </c>
       <c r="F63">
-        <v>1059.765590500662</v>
+        <v>1077.138796902312</v>
       </c>
       <c r="G63">
         <v>138.7</v>
@@ -6447,37 +6447,37 @@
         <v>115.22625</v>
       </c>
       <c r="M63">
-        <v>212.8009305725329</v>
+        <v>216.2894704179843</v>
       </c>
       <c r="N63">
-        <v>-97.57468057253291</v>
+        <v>-101.0632204179843</v>
       </c>
       <c r="O63">
-        <v>-31.22389778321053</v>
+        <v>-32.34023053375498</v>
       </c>
       <c r="P63">
-        <v>-66.35078278932238</v>
+        <v>-68.72298988422932</v>
       </c>
       <c r="Q63">
-        <v>-9.550782789322369</v>
+        <v>-11.92298988422931</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2148047322991508</v>
+        <v>0.2192522252543916</v>
       </c>
       <c r="T63">
-        <v>2.202698216669104</v>
+        <v>2.260663959213027</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1732717986749221</v>
+        <v>0.1704770922446814</v>
       </c>
       <c r="W63">
-        <v>0.1660070228260756</v>
+        <v>0.166568199877268</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5414743708591316</v>
+        <v>0.5327409132646295</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.186588129520575</v>
+        <v>0.188138129520575</v>
       </c>
       <c r="C64">
-        <v>-148.04986022964</v>
+        <v>-174.0300565922305</v>
       </c>
       <c r="D64">
-        <v>790.3889366726722</v>
+        <v>781.7819467117318</v>
       </c>
       <c r="E64">
-        <v>539.2181567372927</v>
+        <v>556.5913631389428</v>
       </c>
       <c r="F64">
-        <v>1077.138796902312</v>
+        <v>1094.512003303962</v>
       </c>
       <c r="G64">
         <v>138.7</v>
@@ -6529,37 +6529,37 @@
         <v>115.22625</v>
       </c>
       <c r="M64">
-        <v>216.2894704179843</v>
+        <v>219.7780102634356</v>
       </c>
       <c r="N64">
-        <v>-101.0632204179843</v>
+        <v>-104.5517602634356</v>
       </c>
       <c r="O64">
-        <v>-32.34023053375498</v>
+        <v>-33.4565632842994</v>
       </c>
       <c r="P64">
-        <v>-68.72298988422932</v>
+        <v>-71.09519697913623</v>
       </c>
       <c r="Q64">
-        <v>-11.92298988422931</v>
+        <v>-14.29519697913622</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2192522252543916</v>
+        <v>0.22394012323424</v>
       </c>
       <c r="T64">
-        <v>2.260663959213027</v>
+        <v>2.321762985137704</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1704770922446814</v>
+        <v>0.167771106653496</v>
       </c>
       <c r="W64">
-        <v>0.166568199877268</v>
+        <v>0.167111561783978</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5327409132646295</v>
+        <v>0.5242847082921751</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.188138129520575</v>
+        <v>0.189688129520575</v>
       </c>
       <c r="C65">
-        <v>-174.0300565922305</v>
+        <v>-199.8248195283961</v>
       </c>
       <c r="D65">
-        <v>781.7819467117318</v>
+        <v>773.3603901772166</v>
       </c>
       <c r="E65">
-        <v>556.5913631389428</v>
+        <v>573.9645695405932</v>
       </c>
       <c r="F65">
-        <v>1094.512003303962</v>
+        <v>1111.885209705613</v>
       </c>
       <c r="G65">
         <v>138.7</v>
@@ -6611,37 +6611,37 @@
         <v>115.22625</v>
       </c>
       <c r="M65">
-        <v>219.7780102634356</v>
+        <v>223.266550108887</v>
       </c>
       <c r="N65">
-        <v>-104.5517602634356</v>
+        <v>-108.040300108887</v>
       </c>
       <c r="O65">
-        <v>-33.4565632842994</v>
+        <v>-34.57289603484385</v>
       </c>
       <c r="P65">
-        <v>-71.09519697913623</v>
+        <v>-73.46740407404319</v>
       </c>
       <c r="Q65">
-        <v>-14.29519697913622</v>
+        <v>-16.66740407404318</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.22394012323424</v>
+        <v>0.2288884599907467</v>
       </c>
       <c r="T65">
-        <v>2.321762985137704</v>
+        <v>2.386256401391529</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.167771106653496</v>
+        <v>0.1651496831120351</v>
       </c>
       <c r="W65">
-        <v>0.167111561783978</v>
+        <v>0.1676379436311033</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5242847082921751</v>
+        <v>0.5160927597251097</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.189688129520575</v>
+        <v>0.191238129520575</v>
       </c>
       <c r="C66">
-        <v>-199.8248195283961</v>
+        <v>-225.4400777821029</v>
       </c>
       <c r="D66">
-        <v>773.3603901772166</v>
+        <v>765.1183383251599</v>
       </c>
       <c r="E66">
-        <v>573.9645695405932</v>
+        <v>591.3377759422433</v>
       </c>
       <c r="F66">
-        <v>1111.885209705613</v>
+        <v>1129.258416107263</v>
       </c>
       <c r="G66">
         <v>138.7</v>
@@ -6693,37 +6693,37 @@
         <v>115.22625</v>
       </c>
       <c r="M66">
-        <v>223.266550108887</v>
+        <v>226.7550899543384</v>
       </c>
       <c r="N66">
-        <v>-108.040300108887</v>
+        <v>-111.5288399543384</v>
       </c>
       <c r="O66">
-        <v>-34.57289603484385</v>
+        <v>-35.68922878538828</v>
       </c>
       <c r="P66">
-        <v>-73.46740407404319</v>
+        <v>-75.83961116895009</v>
       </c>
       <c r="Q66">
-        <v>-16.66740407404318</v>
+        <v>-19.03961116895007</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2288884599907467</v>
+        <v>0.2341195588476252</v>
       </c>
       <c r="T66">
-        <v>2.386256401391529</v>
+        <v>2.454435155717002</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1651496831120351</v>
+        <v>0.1626089187564654</v>
       </c>
       <c r="W66">
-        <v>0.1676379436311033</v>
+        <v>0.1681481291137018</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5160927597251097</v>
+        <v>0.5081528711139542</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.191238129520575</v>
+        <v>0.1927881295205749</v>
       </c>
       <c r="C67">
-        <v>-225.4400777821029</v>
+        <v>-250.8815100212548</v>
       </c>
       <c r="D67">
-        <v>765.1183383251599</v>
+        <v>757.0501124876581</v>
       </c>
       <c r="E67">
-        <v>591.3377759422433</v>
+        <v>608.7109823438934</v>
       </c>
       <c r="F67">
-        <v>1129.258416107263</v>
+        <v>1146.631622508913</v>
       </c>
       <c r="G67">
         <v>138.7</v>
@@ -6775,37 +6775,37 @@
         <v>115.22625</v>
       </c>
       <c r="M67">
-        <v>226.7550899543384</v>
+        <v>230.2436297997897</v>
       </c>
       <c r="N67">
-        <v>-111.5288399543384</v>
+        <v>-115.0173797997897</v>
       </c>
       <c r="O67">
-        <v>-35.68922878538828</v>
+        <v>-36.80556153593271</v>
       </c>
       <c r="P67">
-        <v>-75.83961116895009</v>
+        <v>-78.21181826385701</v>
       </c>
       <c r="Q67">
-        <v>-19.03961116895007</v>
+        <v>-21.411818263857</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2341195588476252</v>
+        <v>0.2396583694019671</v>
       </c>
       <c r="T67">
-        <v>2.454435155717002</v>
+        <v>2.526624425002796</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1626089187564654</v>
+        <v>0.1601451472601553</v>
       </c>
       <c r="W67">
-        <v>0.1681481291137018</v>
+        <v>0.1686428544301608</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5081528711139542</v>
+        <v>0.5004535851879852</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1927881295205749</v>
+        <v>0.2189444019306633</v>
       </c>
       <c r="C68">
-        <v>-250.8815100212548</v>
+        <v>-382.6194244326095</v>
       </c>
       <c r="D68">
-        <v>757.0501124876581</v>
+        <v>642.6854044779536</v>
       </c>
       <c r="E68">
-        <v>608.7109823438934</v>
+        <v>626.0841887455438</v>
       </c>
       <c r="F68">
-        <v>1146.631622508913</v>
+        <v>1164.004828910563</v>
       </c>
       <c r="G68">
         <v>138.7</v>
@@ -6857,45 +6857,45 @@
         <v>115.22625</v>
       </c>
       <c r="M68">
-        <v>230.2436297997897</v>
+        <v>274.4723386571108</v>
       </c>
       <c r="N68">
-        <v>-115.0173797997897</v>
+        <v>-159.2460886571108</v>
       </c>
       <c r="O68">
-        <v>-36.80556153593271</v>
+        <v>-50.95874837027547</v>
       </c>
       <c r="P68">
-        <v>-78.21181826385701</v>
+        <v>-108.2873402868354</v>
       </c>
       <c r="Q68">
-        <v>-21.411818263857</v>
+        <v>-51.48734028683535</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2396583694019671</v>
+        <v>0.2490367212325975</v>
       </c>
       <c r="T68">
-        <v>2.526624425002796</v>
+        <v>2.648855788418463</v>
       </c>
       <c r="U68">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1601451472601553</v>
+        <v>0.1343392204125293</v>
       </c>
       <c r="W68">
-        <v>0.1686428544301608</v>
+        <v>0.2041228118267256</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.5004535851879852</v>
+        <v>0.4198100637891541</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2189444019306633</v>
+        <v>0.2208444019306633</v>
       </c>
       <c r="C69">
-        <v>-382.6194244326095</v>
+        <v>-406.9685881059002</v>
       </c>
       <c r="D69">
-        <v>642.6854044779536</v>
+        <v>635.7094472063133</v>
       </c>
       <c r="E69">
-        <v>626.0841887455438</v>
+        <v>643.4573951471939</v>
       </c>
       <c r="F69">
-        <v>1164.004828910563</v>
+        <v>1181.378035312213</v>
       </c>
       <c r="G69">
         <v>138.7</v>
@@ -6939,37 +6939,37 @@
         <v>115.22625</v>
       </c>
       <c r="M69">
-        <v>274.4723386571108</v>
+        <v>278.5689407266199</v>
       </c>
       <c r="N69">
-        <v>-159.2460886571108</v>
+        <v>-163.3426907266199</v>
       </c>
       <c r="O69">
-        <v>-50.95874837027547</v>
+        <v>-52.26966103251838</v>
       </c>
       <c r="P69">
-        <v>-108.2873402868354</v>
+        <v>-111.0730296941016</v>
       </c>
       <c r="Q69">
-        <v>-51.48734028683535</v>
+        <v>-54.27302969410155</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2490367212325975</v>
+        <v>0.2553878687711161</v>
       </c>
       <c r="T69">
-        <v>2.648855788418463</v>
+        <v>2.73163253180654</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1343392204125293</v>
+        <v>0.1323636436417568</v>
       </c>
       <c r="W69">
-        <v>0.2041228118267256</v>
+        <v>0.2045886528292738</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4198100637891541</v>
+        <v>0.4136363863804901</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2208444019306633</v>
+        <v>0.2227444019306633</v>
       </c>
       <c r="C70">
-        <v>-406.9685881059002</v>
+        <v>-431.1679384064985</v>
       </c>
       <c r="D70">
-        <v>635.7094472063133</v>
+        <v>628.8833033073653</v>
       </c>
       <c r="E70">
-        <v>643.4573951471939</v>
+        <v>660.8306015488442</v>
       </c>
       <c r="F70">
-        <v>1181.378035312213</v>
+        <v>1198.751241713864</v>
       </c>
       <c r="G70">
         <v>138.7</v>
@@ -7021,37 +7021,37 @@
         <v>115.22625</v>
       </c>
       <c r="M70">
-        <v>278.5689407266199</v>
+        <v>282.665542796129</v>
       </c>
       <c r="N70">
-        <v>-163.3426907266199</v>
+        <v>-167.4392927961291</v>
       </c>
       <c r="O70">
-        <v>-52.26966103251838</v>
+        <v>-53.5805736947613</v>
       </c>
       <c r="P70">
-        <v>-111.0730296941016</v>
+        <v>-113.8587191013678</v>
       </c>
       <c r="Q70">
-        <v>-54.27302969410155</v>
+        <v>-57.05871910136774</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2553878687711161</v>
+        <v>0.2621487677637328</v>
       </c>
       <c r="T70">
-        <v>2.73163253180654</v>
+        <v>2.819749710251912</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1323636436417568</v>
+        <v>0.1304453299657893</v>
       </c>
       <c r="W70">
-        <v>0.2045886528292738</v>
+        <v>0.2050409911940669</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4136363863804901</v>
+        <v>0.4076416561430917</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2227444019306633</v>
+        <v>0.2246444019306633</v>
       </c>
       <c r="C71">
-        <v>-431.1679384064985</v>
+        <v>-455.2222500783444</v>
       </c>
       <c r="D71">
-        <v>628.8833033073653</v>
+        <v>622.2021980371695</v>
       </c>
       <c r="E71">
-        <v>660.8306015488442</v>
+        <v>678.2038079504944</v>
       </c>
       <c r="F71">
-        <v>1198.751241713864</v>
+        <v>1216.124448115514</v>
       </c>
       <c r="G71">
         <v>138.7</v>
@@ -7103,37 +7103,37 @@
         <v>115.22625</v>
       </c>
       <c r="M71">
-        <v>282.665542796129</v>
+        <v>286.7621448656382</v>
       </c>
       <c r="N71">
-        <v>-167.4392927961291</v>
+        <v>-171.5358948656382</v>
       </c>
       <c r="O71">
-        <v>-53.5805736947613</v>
+        <v>-54.89148635700422</v>
       </c>
       <c r="P71">
-        <v>-113.8587191013678</v>
+        <v>-116.6444085086339</v>
       </c>
       <c r="Q71">
-        <v>-57.05871910136774</v>
+        <v>-59.84440850863393</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2621487677637328</v>
+        <v>0.2693603933558572</v>
       </c>
       <c r="T71">
-        <v>2.819749710251912</v>
+        <v>2.913741367260309</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1304453299657893</v>
+        <v>0.1285818252519924</v>
       </c>
       <c r="W71">
-        <v>0.2050409911940669</v>
+        <v>0.2054804056055802</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4076416561430917</v>
+        <v>0.401818203912476</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2246444019306633</v>
+        <v>0.2265444019306633</v>
       </c>
       <c r="C72">
-        <v>-455.2222500783444</v>
+        <v>-479.1360970953765</v>
       </c>
       <c r="D72">
-        <v>622.2021980371695</v>
+        <v>615.6615574217875</v>
       </c>
       <c r="E72">
-        <v>678.2038079504944</v>
+        <v>695.5770143521445</v>
       </c>
       <c r="F72">
-        <v>1216.124448115514</v>
+        <v>1233.497654517164</v>
       </c>
       <c r="G72">
         <v>138.7</v>
@@ -7185,37 +7185,37 @@
         <v>115.22625</v>
       </c>
       <c r="M72">
-        <v>286.7621448656382</v>
+        <v>290.8587469351473</v>
       </c>
       <c r="N72">
-        <v>-171.5358948656382</v>
+        <v>-175.6324969351473</v>
       </c>
       <c r="O72">
-        <v>-54.89148635700422</v>
+        <v>-56.20239901924713</v>
       </c>
       <c r="P72">
-        <v>-116.6444085086339</v>
+        <v>-119.4300979159001</v>
       </c>
       <c r="Q72">
-        <v>-59.84440850863393</v>
+        <v>-62.63009791590014</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2693603933558572</v>
+        <v>0.2770693724370937</v>
       </c>
       <c r="T72">
-        <v>2.913741367260309</v>
+        <v>3.014215207510665</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1285818252519924</v>
+        <v>0.1267708136287248</v>
       </c>
       <c r="W72">
-        <v>0.2054804056055802</v>
+        <v>0.2059074421463467</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.401818203912476</v>
+        <v>0.3961587925897652</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2265444019306633</v>
+        <v>0.2284444019306633</v>
       </c>
       <c r="C73">
-        <v>-479.136097095376</v>
+        <v>-502.913863104309</v>
       </c>
       <c r="D73">
-        <v>615.6615574217877</v>
+        <v>609.256997814505</v>
       </c>
       <c r="E73">
-        <v>695.5770143521443</v>
+        <v>712.9502207537946</v>
       </c>
       <c r="F73">
-        <v>1233.497654517164</v>
+        <v>1250.870860918814</v>
       </c>
       <c r="G73">
         <v>138.7</v>
@@ -7267,37 +7267,37 @@
         <v>115.22625</v>
       </c>
       <c r="M73">
-        <v>290.8587469351472</v>
+        <v>294.9553490046563</v>
       </c>
       <c r="N73">
-        <v>-175.6324969351472</v>
+        <v>-179.7290990046563</v>
       </c>
       <c r="O73">
-        <v>-56.20239901924712</v>
+        <v>-57.51331168149003</v>
       </c>
       <c r="P73">
-        <v>-119.4300979159001</v>
+        <v>-122.2157873231663</v>
       </c>
       <c r="Q73">
-        <v>-62.63009791590011</v>
+        <v>-65.41578732316631</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2770693724370936</v>
+        <v>0.2853289928812755</v>
       </c>
       <c r="T73">
-        <v>3.014215207510664</v>
+        <v>3.121865750636045</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1267708136287249</v>
+        <v>0.1250101078838815</v>
       </c>
       <c r="W73">
-        <v>0.2059074421463467</v>
+        <v>0.2063226165609808</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3961587925897652</v>
+        <v>0.3906565871371296</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2284444019306633</v>
+        <v>0.2303444019306633</v>
       </c>
       <c r="C74">
-        <v>-502.913863104309</v>
+        <v>-526.5597512223219</v>
       </c>
       <c r="D74">
-        <v>609.256997814505</v>
+        <v>602.9843160981424</v>
       </c>
       <c r="E74">
-        <v>712.9502207537946</v>
+        <v>730.3234271554447</v>
       </c>
       <c r="F74">
-        <v>1250.870860918814</v>
+        <v>1268.244067320464</v>
       </c>
       <c r="G74">
         <v>138.7</v>
@@ -7349,37 +7349,37 @@
         <v>115.22625</v>
       </c>
       <c r="M74">
-        <v>294.9553490046563</v>
+        <v>299.0519510741655</v>
       </c>
       <c r="N74">
-        <v>-179.7290990046563</v>
+        <v>-183.8257010741655</v>
       </c>
       <c r="O74">
-        <v>-57.51331168149003</v>
+        <v>-58.82422434373295</v>
       </c>
       <c r="P74">
-        <v>-122.2157873231663</v>
+        <v>-125.0014767304325</v>
       </c>
       <c r="Q74">
-        <v>-65.41578732316631</v>
+        <v>-68.2014767304325</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2853289928812755</v>
+        <v>0.2942004370620635</v>
       </c>
       <c r="T74">
-        <v>3.121865750636045</v>
+        <v>3.237490408067009</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1250101078838815</v>
+        <v>0.1232976406525954</v>
       </c>
       <c r="W74">
-        <v>0.2063226165609808</v>
+        <v>0.206726416334118</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3906565871371296</v>
+        <v>0.3853051270393607</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2303444019306633</v>
+        <v>0.2322444019306633</v>
       </c>
       <c r="C75">
-        <v>-526.5597512223219</v>
+        <v>-550.0777932356766</v>
       </c>
       <c r="D75">
-        <v>602.9843160981424</v>
+        <v>596.839480486438</v>
       </c>
       <c r="E75">
-        <v>730.3234271554447</v>
+        <v>747.6966335570951</v>
       </c>
       <c r="F75">
-        <v>1268.244067320464</v>
+        <v>1285.617273722115</v>
       </c>
       <c r="G75">
         <v>138.7</v>
@@ -7431,37 +7431,37 @@
         <v>115.22625</v>
       </c>
       <c r="M75">
-        <v>299.0519510741655</v>
+        <v>303.1485531436746</v>
       </c>
       <c r="N75">
-        <v>-183.8257010741655</v>
+        <v>-187.9223031436746</v>
       </c>
       <c r="O75">
-        <v>-58.82422434373295</v>
+        <v>-60.13513700597588</v>
       </c>
       <c r="P75">
-        <v>-125.0014767304325</v>
+        <v>-127.7871661376988</v>
       </c>
       <c r="Q75">
-        <v>-68.2014767304325</v>
+        <v>-70.98716613769875</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2942004370620635</v>
+        <v>0.303754300025989</v>
       </c>
       <c r="T75">
-        <v>3.237490408067009</v>
+        <v>3.36200926991574</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1232976406525954</v>
+        <v>0.1216314563194522</v>
       </c>
       <c r="W75">
-        <v>0.206726416334118</v>
+        <v>0.2071193025998732</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3853051270393607</v>
+        <v>0.3800983009982881</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2322444019306633</v>
+        <v>0.2341444019306633</v>
       </c>
       <c r="C76">
-        <v>-550.0777932356766</v>
+        <v>-573.4718582415644</v>
       </c>
       <c r="D76">
-        <v>596.839480486438</v>
+        <v>590.8186218822003</v>
       </c>
       <c r="E76">
-        <v>747.6966335570951</v>
+        <v>765.0698399587452</v>
       </c>
       <c r="F76">
-        <v>1285.617273722115</v>
+        <v>1302.990480123765</v>
       </c>
       <c r="G76">
         <v>138.7</v>
@@ -7513,37 +7513,37 @@
         <v>115.22625</v>
       </c>
       <c r="M76">
-        <v>303.1485531436746</v>
+        <v>307.2451552131837</v>
       </c>
       <c r="N76">
-        <v>-187.9223031436746</v>
+        <v>-192.0189052131837</v>
       </c>
       <c r="O76">
-        <v>-60.13513700597588</v>
+        <v>-61.44604966821878</v>
       </c>
       <c r="P76">
-        <v>-127.7871661376988</v>
+        <v>-130.5728555449649</v>
       </c>
       <c r="Q76">
-        <v>-70.98716613769875</v>
+        <v>-73.7728555449649</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.303754300025989</v>
+        <v>0.3140724720270286</v>
       </c>
       <c r="T76">
-        <v>3.36200926991574</v>
+        <v>3.49648964071237</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1216314563194522</v>
+        <v>0.1200097035685262</v>
       </c>
       <c r="W76">
-        <v>0.2071193025998732</v>
+        <v>0.2075017118985415</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3800983009982881</v>
+        <v>0.3750303236516443</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2341444019306633</v>
+        <v>0.2360444019306633</v>
       </c>
       <c r="C77">
-        <v>-573.4718582415644</v>
+        <v>-596.7456607721103</v>
       </c>
       <c r="D77">
-        <v>590.8186218822003</v>
+        <v>584.9180257533044</v>
       </c>
       <c r="E77">
-        <v>765.0698399587452</v>
+        <v>782.4430463603953</v>
       </c>
       <c r="F77">
-        <v>1302.990480123765</v>
+        <v>1320.363686525415</v>
       </c>
       <c r="G77">
         <v>138.7</v>
@@ -7595,37 +7595,37 @@
         <v>115.22625</v>
       </c>
       <c r="M77">
-        <v>307.2451552131837</v>
+        <v>311.3417572826928</v>
       </c>
       <c r="N77">
-        <v>-192.0189052131837</v>
+        <v>-196.1155072826928</v>
       </c>
       <c r="O77">
-        <v>-61.44604966821878</v>
+        <v>-62.7569623304617</v>
       </c>
       <c r="P77">
-        <v>-130.5728555449649</v>
+        <v>-133.3585449522311</v>
       </c>
       <c r="Q77">
-        <v>-73.7728555449649</v>
+        <v>-76.5585449522311</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3140724720270286</v>
+        <v>0.3252504916948215</v>
       </c>
       <c r="T77">
-        <v>3.49648964071237</v>
+        <v>3.642176709075386</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1200097035685262</v>
+        <v>0.1184306285215719</v>
       </c>
       <c r="W77">
-        <v>0.2075017118985415</v>
+        <v>0.2078740577946133</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3750303236516443</v>
+        <v>0.3700957141299123</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2360444019306633</v>
+        <v>0.2379444019306633</v>
       </c>
       <c r="C78">
-        <v>-596.7456607721103</v>
+        <v>-619.9027684363762</v>
       </c>
       <c r="D78">
-        <v>584.9180257533044</v>
+        <v>579.1341244906889</v>
       </c>
       <c r="E78">
-        <v>782.4430463603953</v>
+        <v>799.8162527620457</v>
       </c>
       <c r="F78">
-        <v>1320.363686525415</v>
+        <v>1337.736892927065</v>
       </c>
       <c r="G78">
         <v>138.7</v>
@@ -7677,37 +7677,37 @@
         <v>115.22625</v>
       </c>
       <c r="M78">
-        <v>311.3417572826928</v>
+        <v>315.438359352202</v>
       </c>
       <c r="N78">
-        <v>-196.1155072826928</v>
+        <v>-200.212109352202</v>
       </c>
       <c r="O78">
-        <v>-62.7569623304617</v>
+        <v>-64.06787499270465</v>
       </c>
       <c r="P78">
-        <v>-133.3585449522311</v>
+        <v>-136.1442343594973</v>
       </c>
       <c r="Q78">
-        <v>-76.5585449522311</v>
+        <v>-79.34423435949734</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3252504916948215</v>
+        <v>0.3374005130728572</v>
       </c>
       <c r="T78">
-        <v>3.642176709075386</v>
+        <v>3.80053221816562</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1184306285215719</v>
+        <v>0.1168925684109021</v>
       </c>
       <c r="W78">
-        <v>0.2078740577946133</v>
+        <v>0.2082367323687093</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3700957141299123</v>
+        <v>0.3652892762840692</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2379444019306633</v>
+        <v>0.2398444019306633</v>
       </c>
       <c r="C79">
-        <v>-619.9027684363762</v>
+        <v>-642.9466091133995</v>
       </c>
       <c r="D79">
-        <v>579.1341244906889</v>
+        <v>573.4634902153157</v>
       </c>
       <c r="E79">
-        <v>799.8162527620457</v>
+        <v>817.1894591636958</v>
       </c>
       <c r="F79">
-        <v>1337.736892927065</v>
+        <v>1355.110099328715</v>
       </c>
       <c r="G79">
         <v>138.7</v>
@@ -7759,37 +7759,37 @@
         <v>115.22625</v>
       </c>
       <c r="M79">
-        <v>315.438359352202</v>
+        <v>319.534961421711</v>
       </c>
       <c r="N79">
-        <v>-200.212109352202</v>
+        <v>-204.3087114217111</v>
       </c>
       <c r="O79">
-        <v>-64.06787499270465</v>
+        <v>-65.37878765494754</v>
       </c>
       <c r="P79">
-        <v>-136.1442343594973</v>
+        <v>-138.9299237667635</v>
       </c>
       <c r="Q79">
-        <v>-79.34423435949734</v>
+        <v>-82.12992376676351</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3374005130728572</v>
+        <v>0.3506550818488962</v>
       </c>
       <c r="T79">
-        <v>3.80053221816562</v>
+        <v>3.973283682627693</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1168925684109021</v>
+        <v>0.1153939457389675</v>
       </c>
       <c r="W79">
-        <v>0.2082367323687093</v>
+        <v>0.2085901075947515</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3652892762840692</v>
+        <v>0.3606060804342734</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2398444019306633</v>
+        <v>0.2417444019306633</v>
       </c>
       <c r="C80">
-        <v>-642.9466091133995</v>
+        <v>-665.8804777267455</v>
       </c>
       <c r="D80">
-        <v>573.4634902153157</v>
+        <v>567.90282800362</v>
       </c>
       <c r="E80">
-        <v>817.1894591636958</v>
+        <v>834.5626655653462</v>
       </c>
       <c r="F80">
-        <v>1355.110099328715</v>
+        <v>1372.483305730366</v>
       </c>
       <c r="G80">
         <v>138.7</v>
@@ -7841,37 +7841,37 @@
         <v>115.22625</v>
       </c>
       <c r="M80">
-        <v>319.534961421711</v>
+        <v>323.6315634912202</v>
       </c>
       <c r="N80">
-        <v>-204.3087114217111</v>
+        <v>-208.4053134912202</v>
       </c>
       <c r="O80">
-        <v>-65.37878765494754</v>
+        <v>-66.68970031719047</v>
       </c>
       <c r="P80">
-        <v>-138.9299237667635</v>
+        <v>-141.7156131740298</v>
       </c>
       <c r="Q80">
-        <v>-82.12992376676351</v>
+        <v>-84.91561317402974</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3506550818488962</v>
+        <v>0.3651719905083675</v>
       </c>
       <c r="T80">
-        <v>3.973283682627693</v>
+        <v>4.162487667514728</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1153939457389675</v>
+        <v>0.1139332628815122</v>
       </c>
       <c r="W80">
-        <v>0.2085901075947515</v>
+        <v>0.2089345366125394</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3606060804342734</v>
+        <v>0.3560414465047256</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2417444019306633</v>
+        <v>0.2436444019306633</v>
       </c>
       <c r="C81">
-        <v>-665.8804777267455</v>
+        <v>-688.7075426286985</v>
       </c>
       <c r="D81">
-        <v>567.90282800362</v>
+        <v>562.4489695033172</v>
       </c>
       <c r="E81">
-        <v>834.5626655653462</v>
+        <v>851.9358719669963</v>
       </c>
       <c r="F81">
-        <v>1372.483305730366</v>
+        <v>1389.856512132016</v>
       </c>
       <c r="G81">
         <v>138.7</v>
@@ -7923,37 +7923,37 @@
         <v>115.22625</v>
       </c>
       <c r="M81">
-        <v>323.6315634912202</v>
+        <v>327.7281655607293</v>
       </c>
       <c r="N81">
-        <v>-208.4053134912202</v>
+        <v>-212.5019155607293</v>
       </c>
       <c r="O81">
-        <v>-66.68970031719047</v>
+        <v>-68.00061297943338</v>
       </c>
       <c r="P81">
-        <v>-141.7156131740298</v>
+        <v>-144.501302581296</v>
       </c>
       <c r="Q81">
-        <v>-84.91561317402974</v>
+        <v>-87.70130258129595</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3651719905083675</v>
+        <v>0.3811405900337859</v>
       </c>
       <c r="T81">
-        <v>4.162487667514728</v>
+        <v>4.370612050890464</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1139332628815122</v>
+        <v>0.1125090970954933</v>
       </c>
       <c r="W81">
-        <v>0.2089345366125394</v>
+        <v>0.2092703549048827</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3560414465047256</v>
+        <v>0.3515909284234165</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2436444019306633</v>
+        <v>0.2455444019306633</v>
       </c>
       <c r="C82">
-        <v>-688.7075426286985</v>
+        <v>-711.4308516200933</v>
       </c>
       <c r="D82">
-        <v>562.4489695033172</v>
+        <v>557.0988669135726</v>
       </c>
       <c r="E82">
-        <v>851.9358719669963</v>
+        <v>869.3090783686464</v>
       </c>
       <c r="F82">
-        <v>1389.856512132016</v>
+        <v>1407.229718533666</v>
       </c>
       <c r="G82">
         <v>138.7</v>
@@ -8005,37 +8005,37 @@
         <v>115.22625</v>
       </c>
       <c r="M82">
-        <v>327.7281655607293</v>
+        <v>331.8247676302384</v>
       </c>
       <c r="N82">
-        <v>-212.5019155607293</v>
+        <v>-216.5985176302384</v>
       </c>
       <c r="O82">
-        <v>-68.00061297943338</v>
+        <v>-69.3115256416763</v>
       </c>
       <c r="P82">
-        <v>-144.501302581296</v>
+        <v>-147.2869919885621</v>
       </c>
       <c r="Q82">
-        <v>-87.70130258129595</v>
+        <v>-90.4869919885621</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3811405900337859</v>
+        <v>0.3987900947724061</v>
       </c>
       <c r="T82">
-        <v>4.370612050890464</v>
+        <v>4.600644264095225</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1125090970954933</v>
+        <v>0.1111200958967835</v>
       </c>
       <c r="W82">
-        <v>0.2092703549048827</v>
+        <v>0.2095978813875385</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3515909284234165</v>
+        <v>0.3472502996774485</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2455444019306633</v>
+        <v>0.2474444019306633</v>
       </c>
       <c r="C83">
-        <v>-711.4308516200933</v>
+        <v>-734.0533376298124</v>
       </c>
       <c r="D83">
-        <v>557.0988669135726</v>
+        <v>551.8495873055039</v>
       </c>
       <c r="E83">
-        <v>869.3090783686464</v>
+        <v>886.6822847702967</v>
       </c>
       <c r="F83">
-        <v>1407.229718533666</v>
+        <v>1424.602924935316</v>
       </c>
       <c r="G83">
         <v>138.7</v>
@@ -8087,37 +8087,37 @@
         <v>115.22625</v>
       </c>
       <c r="M83">
-        <v>331.8247676302384</v>
+        <v>335.9213696997476</v>
       </c>
       <c r="N83">
-        <v>-216.5985176302384</v>
+        <v>-220.6951196997476</v>
       </c>
       <c r="O83">
-        <v>-69.3115256416763</v>
+        <v>-70.62243830391922</v>
       </c>
       <c r="P83">
-        <v>-147.2869919885621</v>
+        <v>-150.0726813958283</v>
       </c>
       <c r="Q83">
-        <v>-90.4869919885621</v>
+        <v>-93.27268139582833</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3987900947724061</v>
+        <v>0.4184006555930954</v>
       </c>
       <c r="T83">
-        <v>4.600644264095225</v>
+        <v>4.856235612100516</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1111200958967835</v>
+        <v>0.109764972776091</v>
       </c>
       <c r="W83">
-        <v>0.2095978813875385</v>
+        <v>0.2099174194193978</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3472502996774485</v>
+        <v>0.3430155399252844</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2474444019306633</v>
+        <v>0.2493444019306633</v>
       </c>
       <c r="C84">
-        <v>-734.0533376298124</v>
+        <v>-756.5778240761854</v>
       </c>
       <c r="D84">
-        <v>551.8495873055039</v>
+        <v>546.698307260781</v>
       </c>
       <c r="E84">
-        <v>886.6822847702967</v>
+        <v>904.0554911719469</v>
       </c>
       <c r="F84">
-        <v>1424.602924935316</v>
+        <v>1441.976131336966</v>
       </c>
       <c r="G84">
         <v>138.7</v>
@@ -8169,37 +8169,37 @@
         <v>115.22625</v>
       </c>
       <c r="M84">
-        <v>335.9213696997476</v>
+        <v>340.0179717692567</v>
       </c>
       <c r="N84">
-        <v>-220.6951196997476</v>
+        <v>-224.7917217692567</v>
       </c>
       <c r="O84">
-        <v>-70.62243830391922</v>
+        <v>-71.93335096616214</v>
       </c>
       <c r="P84">
-        <v>-150.0726813958283</v>
+        <v>-152.8583708030945</v>
       </c>
       <c r="Q84">
-        <v>-93.27268139582833</v>
+        <v>-96.05837080309453</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4184006555930954</v>
+        <v>0.4403183412162188</v>
       </c>
       <c r="T84">
-        <v>4.856235612100516</v>
+        <v>5.141896530459371</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.109764972776091</v>
+        <v>0.1084425032245719</v>
       </c>
       <c r="W84">
-        <v>0.2099174194193978</v>
+        <v>0.210229257739646</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3430155399252844</v>
+        <v>0.338882822576787</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2493444019306633</v>
+        <v>0.2512444019306633</v>
       </c>
       <c r="C85">
-        <v>-756.5778240761854</v>
+        <v>-779.0070299308945</v>
       </c>
       <c r="D85">
-        <v>546.698307260781</v>
+        <v>541.6423078077219</v>
       </c>
       <c r="E85">
-        <v>904.0554911719469</v>
+        <v>921.428697573597</v>
       </c>
       <c r="F85">
-        <v>1441.976131336966</v>
+        <v>1459.349337738616</v>
       </c>
       <c r="G85">
         <v>138.7</v>
@@ -8251,37 +8251,37 @@
         <v>115.22625</v>
       </c>
       <c r="M85">
-        <v>340.0179717692567</v>
+        <v>344.1145738387658</v>
       </c>
       <c r="N85">
-        <v>-224.7917217692567</v>
+        <v>-228.8883238387658</v>
       </c>
       <c r="O85">
-        <v>-71.93335096616214</v>
+        <v>-73.24426362840505</v>
       </c>
       <c r="P85">
-        <v>-152.8583708030945</v>
+        <v>-155.6440602103607</v>
       </c>
       <c r="Q85">
-        <v>-96.05837080309453</v>
+        <v>-98.84406021036068</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4403183412162188</v>
+        <v>0.4649757375422325</v>
       </c>
       <c r="T85">
-        <v>5.141896530459371</v>
+        <v>5.463265063613083</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1084425032245719</v>
+        <v>0.107151521043327</v>
       </c>
       <c r="W85">
-        <v>0.210229257739646</v>
+        <v>0.2105336713379835</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.338882822576787</v>
+        <v>0.3348485032603967</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2512444019306633</v>
+        <v>0.2531444019306633</v>
       </c>
       <c r="C86">
-        <v>-779.0070299308945</v>
+        <v>-801.3435745044562</v>
       </c>
       <c r="D86">
-        <v>541.6423078077219</v>
+        <v>536.6789696358103</v>
       </c>
       <c r="E86">
-        <v>921.428697573597</v>
+        <v>938.8019039752471</v>
       </c>
       <c r="F86">
-        <v>1459.349337738616</v>
+        <v>1476.722544140267</v>
       </c>
       <c r="G86">
         <v>138.7</v>
@@ -8333,37 +8333,37 @@
         <v>115.22625</v>
       </c>
       <c r="M86">
-        <v>344.1145738387658</v>
+        <v>348.2111759082749</v>
       </c>
       <c r="N86">
-        <v>-228.8883238387658</v>
+        <v>-232.9849259082749</v>
       </c>
       <c r="O86">
-        <v>-73.24426362840505</v>
+        <v>-74.55517629064796</v>
       </c>
       <c r="P86">
-        <v>-155.6440602103607</v>
+        <v>-158.4297496176269</v>
       </c>
       <c r="Q86">
-        <v>-98.84406021036068</v>
+        <v>-101.6297496176269</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4649757375422322</v>
+        <v>0.4929207867117143</v>
       </c>
       <c r="T86">
-        <v>5.463265063613078</v>
+        <v>5.827482734520617</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.107151521043327</v>
+        <v>0.1058909149134055</v>
       </c>
       <c r="W86">
-        <v>0.2105336713379835</v>
+        <v>0.210830922263419</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3348485032603967</v>
+        <v>0.3309091091043921</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2531444019306633</v>
+        <v>0.2550444019306633</v>
       </c>
       <c r="C87">
-        <v>-801.3435745044562</v>
+        <v>-823.5899819709832</v>
       </c>
       <c r="D87">
-        <v>536.6789696358103</v>
+        <v>531.8057685709334</v>
       </c>
       <c r="E87">
-        <v>938.8019039752471</v>
+        <v>956.1751103768972</v>
       </c>
       <c r="F87">
-        <v>1476.722544140267</v>
+        <v>1494.095750541917</v>
       </c>
       <c r="G87">
         <v>138.7</v>
@@ -8415,37 +8415,37 @@
         <v>115.22625</v>
       </c>
       <c r="M87">
-        <v>348.2111759082749</v>
+        <v>352.307777977784</v>
       </c>
       <c r="N87">
-        <v>-232.9849259082749</v>
+        <v>-237.081527977784</v>
       </c>
       <c r="O87">
-        <v>-74.55517629064796</v>
+        <v>-75.86608895289088</v>
       </c>
       <c r="P87">
-        <v>-158.4297496176269</v>
+        <v>-161.2154390248931</v>
       </c>
       <c r="Q87">
-        <v>-101.6297496176269</v>
+        <v>-104.4154390248931</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4929207867117143</v>
+        <v>0.524857985762551</v>
       </c>
       <c r="T87">
-        <v>5.827482734520617</v>
+        <v>6.243731501272089</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1058909149134055</v>
+        <v>0.1046596252051101</v>
       </c>
       <c r="W87">
-        <v>0.210830922263419</v>
+        <v>0.2111212603766351</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3309091091043921</v>
+        <v>0.3270613287659689</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2550444019306633</v>
+        <v>0.2569444019306633</v>
       </c>
       <c r="C88">
-        <v>-823.5899819709832</v>
+        <v>-845.7486856486476</v>
       </c>
       <c r="D88">
-        <v>531.8057685709334</v>
+        <v>527.0202712949194</v>
       </c>
       <c r="E88">
-        <v>956.1751103768972</v>
+        <v>973.5483167785476</v>
       </c>
       <c r="F88">
-        <v>1494.095750541917</v>
+        <v>1511.468956943567</v>
       </c>
       <c r="G88">
         <v>138.7</v>
@@ -8497,37 +8497,37 @@
         <v>115.22625</v>
       </c>
       <c r="M88">
-        <v>352.307777977784</v>
+        <v>356.4043800472931</v>
       </c>
       <c r="N88">
-        <v>-237.081527977784</v>
+        <v>-241.1781300472931</v>
       </c>
       <c r="O88">
-        <v>-75.86608895289088</v>
+        <v>-77.17700161513379</v>
       </c>
       <c r="P88">
-        <v>-161.2154390248931</v>
+        <v>-164.0011284321593</v>
       </c>
       <c r="Q88">
-        <v>-104.4154390248931</v>
+        <v>-107.2011284321593</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.524857985762551</v>
+        <v>0.561708600051978</v>
       </c>
       <c r="T88">
-        <v>6.243731501272089</v>
+        <v>6.724018539831481</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1046596252051101</v>
+        <v>0.1034566410073502</v>
       </c>
       <c r="W88">
-        <v>0.2111212603766351</v>
+        <v>0.2114049240504668</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3270613287659689</v>
+        <v>0.3233020031479693</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2569444019306633</v>
+        <v>0.2588444019306633</v>
       </c>
       <c r="C89">
-        <v>-845.7486856486476</v>
+        <v>-867.8220320510954</v>
       </c>
       <c r="D89">
-        <v>527.0202712949194</v>
+        <v>522.3201312941217</v>
       </c>
       <c r="E89">
-        <v>973.5483167785476</v>
+        <v>990.9215231801977</v>
       </c>
       <c r="F89">
-        <v>1511.468956943567</v>
+        <v>1528.842163345217</v>
       </c>
       <c r="G89">
         <v>138.7</v>
@@ -8579,37 +8579,37 @@
         <v>115.22625</v>
       </c>
       <c r="M89">
-        <v>356.4043800472931</v>
+        <v>360.5009821168022</v>
       </c>
       <c r="N89">
-        <v>-241.1781300472931</v>
+        <v>-245.2747321168022</v>
       </c>
       <c r="O89">
-        <v>-77.17700161513379</v>
+        <v>-78.48791427737672</v>
       </c>
       <c r="P89">
-        <v>-164.0011284321593</v>
+        <v>-166.7868178394255</v>
       </c>
       <c r="Q89">
-        <v>-107.2011284321593</v>
+        <v>-109.9868178394255</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.561708600051978</v>
+        <v>0.604700983389643</v>
       </c>
       <c r="T89">
-        <v>6.724018539831481</v>
+        <v>7.284353418150772</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1034566410073502</v>
+        <v>0.1022809973595394</v>
       </c>
       <c r="W89">
-        <v>0.2114049240504668</v>
+        <v>0.2116821408226206</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3233020031479693</v>
+        <v>0.3196281167485605</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2588444019306633</v>
+        <v>0.2607444019306633</v>
       </c>
       <c r="C90">
-        <v>-867.8220320510954</v>
+        <v>-889.8122847239902</v>
       </c>
       <c r="D90">
-        <v>522.3201312941217</v>
+        <v>517.7030850228773</v>
       </c>
       <c r="E90">
-        <v>990.9215231801977</v>
+        <v>1008.294729581848</v>
       </c>
       <c r="F90">
-        <v>1528.842163345217</v>
+        <v>1546.215369746868</v>
       </c>
       <c r="G90">
         <v>138.7</v>
@@ -8661,37 +8661,37 @@
         <v>115.22625</v>
       </c>
       <c r="M90">
-        <v>360.5009821168022</v>
+        <v>364.5975841863114</v>
       </c>
       <c r="N90">
-        <v>-245.2747321168022</v>
+        <v>-249.3713341863114</v>
       </c>
       <c r="O90">
-        <v>-78.48791427737672</v>
+        <v>-79.79882693961964</v>
       </c>
       <c r="P90">
-        <v>-166.7868178394255</v>
+        <v>-169.5725072466918</v>
       </c>
       <c r="Q90">
-        <v>-109.9868178394255</v>
+        <v>-112.7725072466918</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.604700983389643</v>
+        <v>0.6555101636977924</v>
       </c>
       <c r="T90">
-        <v>7.284353418150772</v>
+        <v>7.946567365255388</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1022809973595394</v>
+        <v>0.1011317726701063</v>
       </c>
       <c r="W90">
-        <v>0.2116821408226206</v>
+        <v>0.211953128004389</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3196281167485605</v>
+        <v>0.3160367895940823</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2607444019306633</v>
+        <v>0.2626444019306633</v>
       </c>
       <c r="C91">
-        <v>-889.8122847239902</v>
+        <v>-911.7216278798553</v>
       </c>
       <c r="D91">
-        <v>517.7030850228773</v>
+        <v>513.1669482686623</v>
       </c>
       <c r="E91">
-        <v>1008.294729581848</v>
+        <v>1025.667935983498</v>
       </c>
       <c r="F91">
-        <v>1546.215369746868</v>
+        <v>1563.588576148518</v>
       </c>
       <c r="G91">
         <v>138.7</v>
@@ -8743,37 +8743,37 @@
         <v>115.22625</v>
       </c>
       <c r="M91">
-        <v>364.5975841863114</v>
+        <v>368.6941862558205</v>
       </c>
       <c r="N91">
-        <v>-249.3713341863114</v>
+        <v>-253.4679362558205</v>
       </c>
       <c r="O91">
-        <v>-79.79882693961964</v>
+        <v>-81.10973960186254</v>
       </c>
       <c r="P91">
-        <v>-169.5725072466918</v>
+        <v>-172.3581966539579</v>
       </c>
       <c r="Q91">
-        <v>-112.7725072466918</v>
+        <v>-115.5581966539579</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6555101636977924</v>
+        <v>0.7164811800675717</v>
       </c>
       <c r="T91">
-        <v>7.946567365255388</v>
+        <v>8.741224101780928</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1011317726701063</v>
+        <v>0.1000080863071052</v>
       </c>
       <c r="W91">
-        <v>0.211953128004389</v>
+        <v>0.2122180932487846</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3160367895940823</v>
+        <v>0.3125252697097036</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2626444019306633</v>
+        <v>0.2645444019306633</v>
       </c>
       <c r="C92">
-        <v>-911.7216278798553</v>
+        <v>-933.5521698434895</v>
       </c>
       <c r="D92">
-        <v>513.1669482686623</v>
+        <v>508.7096127066783</v>
       </c>
       <c r="E92">
-        <v>1025.667935983498</v>
+        <v>1043.041142385148</v>
       </c>
       <c r="F92">
-        <v>1563.588576148518</v>
+        <v>1580.961782550168</v>
       </c>
       <c r="G92">
         <v>138.7</v>
@@ -8825,37 +8825,37 @@
         <v>115.22625</v>
       </c>
       <c r="M92">
-        <v>368.6941862558205</v>
+        <v>372.7907883253296</v>
       </c>
       <c r="N92">
-        <v>-253.4679362558205</v>
+        <v>-257.5645383253296</v>
       </c>
       <c r="O92">
-        <v>-81.10973960186254</v>
+        <v>-82.42065226410547</v>
       </c>
       <c r="P92">
-        <v>-172.3581966539579</v>
+        <v>-175.1438860612241</v>
       </c>
       <c r="Q92">
-        <v>-115.5581966539579</v>
+        <v>-118.3438860612241</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7164811800675717</v>
+        <v>0.7910013111861908</v>
       </c>
       <c r="T92">
-        <v>8.741224101780928</v>
+        <v>9.712471224201032</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1000080863071052</v>
+        <v>0.09890909634768642</v>
       </c>
       <c r="W92">
-        <v>0.2122180932487846</v>
+        <v>0.2124772350812155</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3125252697097036</v>
+        <v>0.3090909260865201</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2645444019306633</v>
+        <v>0.2664444019306633</v>
       </c>
       <c r="C93">
-        <v>-933.5521698434895</v>
+        <v>-955.3059463193647</v>
       </c>
       <c r="D93">
-        <v>508.7096127066783</v>
+        <v>504.3290426324534</v>
       </c>
       <c r="E93">
-        <v>1043.041142385148</v>
+        <v>1060.414348786799</v>
       </c>
       <c r="F93">
-        <v>1580.961782550168</v>
+        <v>1598.334988951818</v>
       </c>
       <c r="G93">
         <v>138.7</v>
@@ -8907,37 +8907,37 @@
         <v>115.22625</v>
       </c>
       <c r="M93">
-        <v>372.7907883253296</v>
+        <v>376.8873903948387</v>
       </c>
       <c r="N93">
-        <v>-257.5645383253296</v>
+        <v>-261.6611403948388</v>
       </c>
       <c r="O93">
-        <v>-82.42065226410547</v>
+        <v>-83.7315649263484</v>
       </c>
       <c r="P93">
-        <v>-175.1438860612241</v>
+        <v>-177.9295754684904</v>
       </c>
       <c r="Q93">
-        <v>-118.3438860612241</v>
+        <v>-121.1295754684903</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7910013111861908</v>
+        <v>0.884151475084465</v>
       </c>
       <c r="T93">
-        <v>9.712471224201032</v>
+        <v>10.92653012722617</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09890909634768642</v>
+        <v>0.09783399747434199</v>
       </c>
       <c r="W93">
-        <v>0.2124772350812155</v>
+        <v>0.2127307433955502</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3090909260865201</v>
+        <v>0.3057312421073187</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2664444019306633</v>
+        <v>0.2683444019306633</v>
       </c>
       <c r="C94">
-        <v>-955.3059463193647</v>
+        <v>-976.9849234916506</v>
       </c>
       <c r="D94">
-        <v>504.3290426324534</v>
+        <v>500.0232718618176</v>
       </c>
       <c r="E94">
-        <v>1060.414348786799</v>
+        <v>1077.787555188449</v>
       </c>
       <c r="F94">
-        <v>1598.334988951818</v>
+        <v>1615.708195353468</v>
       </c>
       <c r="G94">
         <v>138.7</v>
@@ -8989,37 +8989,37 @@
         <v>115.22625</v>
       </c>
       <c r="M94">
-        <v>376.8873903948387</v>
+        <v>380.9839924643478</v>
       </c>
       <c r="N94">
-        <v>-261.6611403948388</v>
+        <v>-265.7577424643478</v>
       </c>
       <c r="O94">
-        <v>-83.7315649263484</v>
+        <v>-85.0424775885913</v>
       </c>
       <c r="P94">
-        <v>-177.9295754684904</v>
+        <v>-180.7152648757565</v>
       </c>
       <c r="Q94">
-        <v>-121.1295754684903</v>
+        <v>-123.9152648757565</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.884151475084465</v>
+        <v>1.003915971525103</v>
       </c>
       <c r="T94">
-        <v>10.92653012722617</v>
+        <v>12.48746300254419</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09783399747434199</v>
+        <v>0.09678201900687597</v>
       </c>
       <c r="W94">
-        <v>0.2127307433955502</v>
+        <v>0.2129787999181786</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3057312421073187</v>
+        <v>0.3024438093964874</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2683444019306633</v>
+        <v>0.2702444019306633</v>
       </c>
       <c r="C95">
-        <v>-976.9849234916506</v>
+        <v>-998.5910009667837</v>
       </c>
       <c r="D95">
-        <v>500.0232718618176</v>
+        <v>495.7904007883349</v>
       </c>
       <c r="E95">
-        <v>1077.787555188449</v>
+        <v>1095.160761590099</v>
       </c>
       <c r="F95">
-        <v>1615.708195353468</v>
+        <v>1633.081401755119</v>
       </c>
       <c r="G95">
         <v>138.7</v>
@@ -9071,37 +9071,37 @@
         <v>115.22625</v>
       </c>
       <c r="M95">
-        <v>380.9839924643478</v>
+        <v>385.080594533857</v>
       </c>
       <c r="N95">
-        <v>-265.7577424643478</v>
+        <v>-269.854344533857</v>
       </c>
       <c r="O95">
-        <v>-85.0424775885913</v>
+        <v>-86.35339025083424</v>
       </c>
       <c r="P95">
-        <v>-180.7152648757565</v>
+        <v>-183.5009542830227</v>
       </c>
       <c r="Q95">
-        <v>-123.9152648757565</v>
+        <v>-126.7009542830227</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.003915971525103</v>
+        <v>1.163601966779287</v>
       </c>
       <c r="T95">
-        <v>12.48746300254419</v>
+        <v>14.56870683630156</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09678201900687597</v>
+        <v>0.0957524230599943</v>
       </c>
       <c r="W95">
-        <v>0.2129787999181786</v>
+        <v>0.2132215786424533</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3024438093964874</v>
+        <v>0.2992263220624821</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2702444019306633</v>
+        <v>0.2721444019306633</v>
       </c>
       <c r="C96">
-        <v>-998.5910009667837</v>
+        <v>-1020.126014567829</v>
       </c>
       <c r="D96">
-        <v>495.7904007883349</v>
+        <v>491.6285935889398</v>
       </c>
       <c r="E96">
-        <v>1095.160761590099</v>
+        <v>1112.533967991749</v>
       </c>
       <c r="F96">
-        <v>1633.081401755119</v>
+        <v>1650.454608156769</v>
       </c>
       <c r="G96">
         <v>138.7</v>
@@ -9153,37 +9153,37 @@
         <v>115.22625</v>
       </c>
       <c r="M96">
-        <v>385.080594533857</v>
+        <v>389.1771966033661</v>
       </c>
       <c r="N96">
-        <v>-269.854344533857</v>
+        <v>-273.9509466033661</v>
       </c>
       <c r="O96">
-        <v>-86.35339025083424</v>
+        <v>-87.66430291307715</v>
       </c>
       <c r="P96">
-        <v>-183.5009542830227</v>
+        <v>-186.2866436902889</v>
       </c>
       <c r="Q96">
-        <v>-126.7009542830227</v>
+        <v>-129.4866436902889</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.163601966779287</v>
+        <v>1.387162360135145</v>
       </c>
       <c r="T96">
-        <v>14.56870683630156</v>
+        <v>17.48244820356187</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0957524230599943</v>
+        <v>0.09474450281725752</v>
       </c>
       <c r="W96">
-        <v>0.2132215786424533</v>
+        <v>0.2134592462356907</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2992263220624821</v>
+        <v>0.2960765713039297</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2721444019306633</v>
+        <v>0.2740444019306633</v>
       </c>
       <c r="C97">
-        <v>-1020.126014567829</v>
+        <v>-1041.591738989276</v>
       </c>
       <c r="D97">
-        <v>491.6285935889398</v>
+        <v>487.536075569143</v>
       </c>
       <c r="E97">
-        <v>1112.533967991749</v>
+        <v>1129.907174393399</v>
       </c>
       <c r="F97">
-        <v>1650.454608156769</v>
+        <v>1667.827814558419</v>
       </c>
       <c r="G97">
         <v>138.7</v>
@@ -9235,37 +9235,37 @@
         <v>115.22625</v>
       </c>
       <c r="M97">
-        <v>389.1771966033661</v>
+        <v>393.2737986728752</v>
       </c>
       <c r="N97">
-        <v>-273.9509466033661</v>
+        <v>-278.0475486728752</v>
       </c>
       <c r="O97">
-        <v>-87.66430291307715</v>
+        <v>-88.97521557532005</v>
       </c>
       <c r="P97">
-        <v>-186.2866436902889</v>
+        <v>-189.0723330975551</v>
       </c>
       <c r="Q97">
-        <v>-129.4866436902889</v>
+        <v>-132.2723330975551</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.387162360135145</v>
+        <v>1.722502950168932</v>
       </c>
       <c r="T97">
-        <v>17.48244820356187</v>
+        <v>21.85306025445236</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09474450281725752</v>
+        <v>0.09375758091291109</v>
       </c>
       <c r="W97">
-        <v>0.2134592462356907</v>
+        <v>0.2136919624207356</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2960765713039297</v>
+        <v>0.2929924403528471</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2740444019306633</v>
+        <v>0.2759444019306633</v>
       </c>
       <c r="C98">
-        <v>-1041.591738989276</v>
+        <v>-1062.989890320329</v>
       </c>
       <c r="D98">
-        <v>487.536075569143</v>
+        <v>483.5111306397396</v>
       </c>
       <c r="E98">
-        <v>1129.907174393399</v>
+        <v>1147.280380795049</v>
       </c>
       <c r="F98">
-        <v>1667.827814558419</v>
+        <v>1685.201020960069</v>
       </c>
       <c r="G98">
         <v>138.7</v>
@@ -9317,37 +9317,37 @@
         <v>115.22625</v>
       </c>
       <c r="M98">
-        <v>393.2737986728751</v>
+        <v>397.3704007423843</v>
       </c>
       <c r="N98">
-        <v>-278.0475486728751</v>
+        <v>-282.1441507423843</v>
       </c>
       <c r="O98">
-        <v>-88.97521557532004</v>
+        <v>-90.28612823756298</v>
       </c>
       <c r="P98">
-        <v>-189.0723330975551</v>
+        <v>-191.8580225048213</v>
       </c>
       <c r="Q98">
-        <v>-132.2723330975551</v>
+        <v>-135.0580225048213</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.722502950168928</v>
+        <v>2.28140393355857</v>
       </c>
       <c r="T98">
-        <v>21.85306025445229</v>
+        <v>29.13741367260306</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09375758091291111</v>
+        <v>0.09279100791380891</v>
       </c>
       <c r="W98">
-        <v>0.2136919624207356</v>
+        <v>0.2139198803339239</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2929924403528472</v>
+        <v>0.2899718997306528</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2759444019306633</v>
+        <v>0.2778444019306633</v>
       </c>
       <c r="C99">
-        <v>-1062.989890320329</v>
+        <v>-1084.322128444236</v>
       </c>
       <c r="D99">
-        <v>483.5111306397396</v>
+        <v>479.5520989174833</v>
       </c>
       <c r="E99">
-        <v>1147.280380795049</v>
+        <v>1164.6535871967</v>
       </c>
       <c r="F99">
-        <v>1685.201020960069</v>
+        <v>1702.574227361719</v>
       </c>
       <c r="G99">
         <v>138.7</v>
@@ -9399,37 +9399,37 @@
         <v>115.22625</v>
       </c>
       <c r="M99">
-        <v>397.3704007423843</v>
+        <v>401.4670028118934</v>
       </c>
       <c r="N99">
-        <v>-282.1441507423843</v>
+        <v>-286.2407528118934</v>
       </c>
       <c r="O99">
-        <v>-90.28612823756298</v>
+        <v>-91.59704089980589</v>
       </c>
       <c r="P99">
-        <v>-191.8580225048213</v>
+        <v>-194.6437119120875</v>
       </c>
       <c r="Q99">
-        <v>-135.0580225048213</v>
+        <v>-137.8437119120875</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.28140393355857</v>
+        <v>3.399205900337855</v>
       </c>
       <c r="T99">
-        <v>29.13741367260306</v>
+        <v>43.70612050890459</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09279100791380891</v>
+        <v>0.09184416089428026</v>
       </c>
       <c r="W99">
-        <v>0.2139198803339239</v>
+        <v>0.2141431468611287</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2899718997306528</v>
+        <v>0.2870130027946258</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2778444019306633</v>
+        <v>0.2797444019306633</v>
       </c>
       <c r="C100">
-        <v>-1084.322128444236</v>
+        <v>-1105.590059320692</v>
       </c>
       <c r="D100">
-        <v>479.5520989174833</v>
+        <v>475.6573744426772</v>
       </c>
       <c r="E100">
-        <v>1164.6535871967</v>
+        <v>1182.02679359835</v>
       </c>
       <c r="F100">
-        <v>1702.574227361719</v>
+        <v>1719.947433763369</v>
       </c>
       <c r="G100">
         <v>138.7</v>
@@ -9481,37 +9481,37 @@
         <v>115.22625</v>
       </c>
       <c r="M100">
-        <v>401.4670028118934</v>
+        <v>405.5636048814025</v>
       </c>
       <c r="N100">
-        <v>-286.2407528118934</v>
+        <v>-290.3373548814025</v>
       </c>
       <c r="O100">
-        <v>-91.59704089980589</v>
+        <v>-92.9079535620488</v>
       </c>
       <c r="P100">
-        <v>-194.6437119120875</v>
+        <v>-197.4294013193537</v>
       </c>
       <c r="Q100">
-        <v>-137.8437119120875</v>
+        <v>-140.6294013193537</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.399205900337855</v>
+        <v>6.75261180067571</v>
       </c>
       <c r="T100">
-        <v>43.70612050890459</v>
+        <v>87.41224101780918</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09184416089428026</v>
+        <v>0.09091644209736834</v>
       </c>
       <c r="W100">
-        <v>0.2141431468611287</v>
+        <v>0.2143619029534405</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2870130027946258</v>
+        <v>0.284113881554276</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2797444019306633</v>
-      </c>
-      <c r="C101">
-        <v>-1105.590059320692</v>
-      </c>
-      <c r="D101">
-        <v>475.6573744426772</v>
-      </c>
-      <c r="E101">
-        <v>1182.02679359835</v>
-      </c>
-      <c r="F101">
-        <v>1719.947433763369</v>
-      </c>
-      <c r="G101">
-        <v>138.7</v>
-      </c>
-      <c r="H101">
-        <v>1199.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>172.02625</v>
-      </c>
-      <c r="K101">
-        <v>56.80000000000001</v>
-      </c>
-      <c r="L101">
-        <v>115.22625</v>
-      </c>
-      <c r="M101">
-        <v>405.5636048814025</v>
-      </c>
-      <c r="N101">
-        <v>-290.3373548814025</v>
-      </c>
-      <c r="O101">
-        <v>-92.9079535620488</v>
-      </c>
-      <c r="P101">
-        <v>-197.4294013193537</v>
-      </c>
-      <c r="Q101">
-        <v>-140.6294013193537</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.75261180067571</v>
-      </c>
-      <c r="T101">
-        <v>87.41224101780918</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09091644209736834</v>
-      </c>
-      <c r="W101">
-        <v>0.2143619029534405</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.284113881554276</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
